--- a/research/traditional_assets/database/data/norway/norway_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_real_estate_development.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06510040018055784</v>
+        <v>0.0649922793001606</v>
       </c>
       <c r="C2">
-        <v>398.7087124281169</v>
+        <v>395.3581913488698</v>
       </c>
       <c r="D2">
-        <v>380.7087124281169</v>
+        <v>381.6041913488698</v>
       </c>
       <c r="E2">
-        <v>-129.2</v>
+        <v>-124.954</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.246</v>
       </c>
       <c r="G2">
         <v>18</v>
@@ -1451,28 +1451,28 @@
         <v>21.483</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2135738</v>
       </c>
       <c r="N2">
-        <v>21.483</v>
+        <v>21.2694262</v>
       </c>
       <c r="O2">
-        <v>4.726259999999999</v>
+        <v>4.679273764</v>
       </c>
       <c r="P2">
-        <v>16.75674</v>
+        <v>16.590152436</v>
       </c>
       <c r="Q2">
-        <v>17.67374</v>
+        <v>17.507152436</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06510040018055784</v>
+        <v>0.06525246393955617</v>
       </c>
       <c r="T2">
-        <v>0.4457367247241993</v>
+        <v>0.4492485898280869</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>100.5881807599996</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0649922793001606</v>
+        <v>0.06488415841976337</v>
       </c>
       <c r="C3">
-        <v>395.3581913488698</v>
+        <v>392.0118927791445</v>
       </c>
       <c r="D3">
-        <v>381.6041913488698</v>
+        <v>382.5038927791445</v>
       </c>
       <c r="E3">
-        <v>-124.954</v>
+        <v>-120.708</v>
       </c>
       <c r="F3">
-        <v>4.246</v>
+        <v>8.491999999999999</v>
       </c>
       <c r="G3">
         <v>18</v>
@@ -1533,28 +1533,28 @@
         <v>21.483</v>
       </c>
       <c r="M3">
-        <v>0.2135738</v>
+        <v>0.4271476</v>
       </c>
       <c r="N3">
-        <v>21.2694262</v>
+        <v>21.0558524</v>
       </c>
       <c r="O3">
-        <v>4.679273764</v>
+        <v>4.632287527999999</v>
       </c>
       <c r="P3">
-        <v>16.590152436</v>
+        <v>16.423564872</v>
       </c>
       <c r="Q3">
-        <v>17.507152436</v>
+        <v>17.340564872</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06525246393955617</v>
+        <v>0.06540763104057487</v>
       </c>
       <c r="T3">
-        <v>0.4492485898280869</v>
+        <v>0.4528321256483804</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>100.5881807599996</v>
+        <v>50.29409037999979</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06488415841976337</v>
+        <v>0.06477603753936616</v>
       </c>
       <c r="C4">
-        <v>392.0118927791445</v>
+        <v>388.6698466555293</v>
       </c>
       <c r="D4">
-        <v>382.5038927791445</v>
+        <v>383.4078466555293</v>
       </c>
       <c r="E4">
-        <v>-120.708</v>
+        <v>-116.462</v>
       </c>
       <c r="F4">
-        <v>8.491999999999999</v>
+        <v>12.738</v>
       </c>
       <c r="G4">
         <v>18</v>
@@ -1615,28 +1615,28 @@
         <v>21.483</v>
       </c>
       <c r="M4">
-        <v>0.4271476</v>
+        <v>0.6407213999999999</v>
       </c>
       <c r="N4">
-        <v>21.0558524</v>
+        <v>20.8422786</v>
       </c>
       <c r="O4">
-        <v>4.632287527999999</v>
+        <v>4.585301292</v>
       </c>
       <c r="P4">
-        <v>16.423564872</v>
+        <v>16.256977308</v>
       </c>
       <c r="Q4">
-        <v>17.340564872</v>
+        <v>17.173977308</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06540763104057487</v>
+        <v>0.06556599746326408</v>
       </c>
       <c r="T4">
-        <v>0.4528321256483804</v>
+        <v>0.4564895488051748</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>50.29409037999979</v>
+        <v>33.52939358666653</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06477603753936616</v>
+        <v>0.06466791665896893</v>
       </c>
       <c r="C5">
-        <v>388.6698466555293</v>
+        <v>385.3320831982741</v>
       </c>
       <c r="D5">
-        <v>383.4078466555293</v>
+        <v>384.316083198274</v>
       </c>
       <c r="E5">
-        <v>-116.462</v>
+        <v>-112.216</v>
       </c>
       <c r="F5">
-        <v>12.738</v>
+        <v>16.984</v>
       </c>
       <c r="G5">
         <v>18</v>
@@ -1697,28 +1697,28 @@
         <v>21.483</v>
       </c>
       <c r="M5">
-        <v>0.6407213999999999</v>
+        <v>0.8542951999999999</v>
       </c>
       <c r="N5">
-        <v>20.8422786</v>
+        <v>20.6287048</v>
       </c>
       <c r="O5">
-        <v>4.585301292</v>
+        <v>4.538315055999999</v>
       </c>
       <c r="P5">
-        <v>16.256977308</v>
+        <v>16.090389744</v>
       </c>
       <c r="Q5">
-        <v>17.173977308</v>
+        <v>17.007389744</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06556599746326408</v>
+        <v>0.06572766318642596</v>
       </c>
       <c r="T5">
-        <v>0.4564895488051748</v>
+        <v>0.4602231682777357</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>33.52939358666653</v>
+        <v>25.1470451899999</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06466791665896893</v>
+        <v>0.0645597957785717</v>
       </c>
       <c r="C6">
-        <v>385.3320831982741</v>
+        <v>381.9986329146575</v>
       </c>
       <c r="D6">
-        <v>384.316083198274</v>
+        <v>385.2286329146575</v>
       </c>
       <c r="E6">
-        <v>-112.216</v>
+        <v>-107.97</v>
       </c>
       <c r="F6">
-        <v>16.984</v>
+        <v>21.23</v>
       </c>
       <c r="G6">
         <v>18</v>
@@ -1779,28 +1779,28 @@
         <v>21.483</v>
       </c>
       <c r="M6">
-        <v>0.8542951999999999</v>
+        <v>1.067869</v>
       </c>
       <c r="N6">
-        <v>20.6287048</v>
+        <v>20.415131</v>
       </c>
       <c r="O6">
-        <v>4.538315055999999</v>
+        <v>4.491328819999999</v>
       </c>
       <c r="P6">
-        <v>16.090389744</v>
+        <v>15.92380218</v>
       </c>
       <c r="Q6">
-        <v>17.007389744</v>
+        <v>16.84080218</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06572766318642596</v>
+        <v>0.06589273239849652</v>
       </c>
       <c r="T6">
-        <v>0.4602231682777357</v>
+        <v>0.4640353902655086</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>25.1470451899999</v>
+        <v>20.11763615199991</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0645597957785717</v>
+        <v>0.06445167489817447</v>
       </c>
       <c r="C7">
-        <v>381.9986329146575</v>
+        <v>378.6695266024035</v>
       </c>
       <c r="D7">
-        <v>385.2286329146575</v>
+        <v>386.1455266024035</v>
       </c>
       <c r="E7">
-        <v>-107.97</v>
+        <v>-103.724</v>
       </c>
       <c r="F7">
-        <v>21.23</v>
+        <v>25.476</v>
       </c>
       <c r="G7">
         <v>18</v>
@@ -1861,28 +1861,28 @@
         <v>21.483</v>
       </c>
       <c r="M7">
-        <v>1.067869</v>
+        <v>1.2814428</v>
       </c>
       <c r="N7">
-        <v>20.415131</v>
+        <v>20.2015572</v>
       </c>
       <c r="O7">
-        <v>4.491328819999999</v>
+        <v>4.444342583999999</v>
       </c>
       <c r="P7">
-        <v>15.92380218</v>
+        <v>15.757214616</v>
       </c>
       <c r="Q7">
-        <v>16.84080218</v>
+        <v>16.674214616</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06589273239849652</v>
+        <v>0.06606131372146221</v>
       </c>
       <c r="T7">
-        <v>0.4640353902655086</v>
+        <v>0.4679287233594041</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.11763615199991</v>
+        <v>16.76469679333326</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06445167489817447</v>
+        <v>0.06434355401777725</v>
       </c>
       <c r="C8">
-        <v>378.6695266024035</v>
+        <v>375.3447953531455</v>
       </c>
       <c r="D8">
-        <v>386.1455266024035</v>
+        <v>387.0667953531455</v>
       </c>
       <c r="E8">
-        <v>-103.724</v>
+        <v>-99.47799999999999</v>
       </c>
       <c r="F8">
-        <v>25.476</v>
+        <v>29.72199999999999</v>
       </c>
       <c r="G8">
         <v>18</v>
@@ -1943,28 +1943,28 @@
         <v>21.483</v>
       </c>
       <c r="M8">
-        <v>1.2814428</v>
+        <v>1.4950166</v>
       </c>
       <c r="N8">
-        <v>20.2015572</v>
+        <v>19.9879834</v>
       </c>
       <c r="O8">
-        <v>4.444342583999999</v>
+        <v>4.397356348</v>
       </c>
       <c r="P8">
-        <v>15.757214616</v>
+        <v>15.590627052</v>
       </c>
       <c r="Q8">
-        <v>16.674214616</v>
+        <v>16.507627052</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06606131372146221</v>
+        <v>0.06623352044922284</v>
       </c>
       <c r="T8">
-        <v>0.4679287233594041</v>
+        <v>0.4719057840467167</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.76469679333326</v>
+        <v>14.36974010857137</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06434355401777725</v>
+        <v>0.06432903313738002</v>
       </c>
       <c r="C9">
-        <v>375.3447953531455</v>
+        <v>371.2228587884699</v>
       </c>
       <c r="D9">
-        <v>387.0667953531455</v>
+        <v>387.1908587884699</v>
       </c>
       <c r="E9">
-        <v>-99.47799999999998</v>
+        <v>-95.232</v>
       </c>
       <c r="F9">
-        <v>29.722</v>
+        <v>33.968</v>
       </c>
       <c r="G9">
         <v>18</v>
@@ -2025,45 +2025,45 @@
         <v>21.483</v>
       </c>
       <c r="M9">
-        <v>1.4950166</v>
+        <v>1.7595424</v>
       </c>
       <c r="N9">
-        <v>19.9879834</v>
+        <v>19.7234576</v>
       </c>
       <c r="O9">
-        <v>4.397356348</v>
+        <v>4.339160671999999</v>
       </c>
       <c r="P9">
-        <v>15.590627052</v>
+        <v>15.384296928</v>
       </c>
       <c r="Q9">
-        <v>16.507627052</v>
+        <v>16.301296928</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06623352044922284</v>
+        <v>0.06640947080150002</v>
       </c>
       <c r="T9">
-        <v>0.4719057840467168</v>
+        <v>0.475969302575058</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>14.36974010857137</v>
+        <v>12.20942445035709</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06432903313738002</v>
+        <v>0.0642326122569828</v>
       </c>
       <c r="C10">
-        <v>371.2228587884699</v>
+        <v>367.8026807465542</v>
       </c>
       <c r="D10">
-        <v>387.1908587884699</v>
+        <v>388.0166807465542</v>
       </c>
       <c r="E10">
-        <v>-95.232</v>
+        <v>-90.98599999999999</v>
       </c>
       <c r="F10">
-        <v>33.968</v>
+        <v>38.214</v>
       </c>
       <c r="G10">
         <v>18</v>
@@ -2107,28 +2107,28 @@
         <v>21.483</v>
       </c>
       <c r="M10">
-        <v>1.7595424</v>
+        <v>1.9794852</v>
       </c>
       <c r="N10">
-        <v>19.7234576</v>
+        <v>19.5035148</v>
       </c>
       <c r="O10">
-        <v>4.339160671999999</v>
+        <v>4.290773256</v>
       </c>
       <c r="P10">
-        <v>15.384296928</v>
+        <v>15.212741544</v>
       </c>
       <c r="Q10">
-        <v>16.301296928</v>
+        <v>16.129741544</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.06640947080150002</v>
+        <v>0.06658928819448659</v>
       </c>
       <c r="T10">
-        <v>0.475969302575058</v>
+        <v>0.4801221292029232</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>12.20942445035709</v>
+        <v>10.85282173365075</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0642326122569828</v>
+        <v>0.06426879137658556</v>
       </c>
       <c r="C11">
-        <v>367.8026807465542</v>
+        <v>363.2464025878058</v>
       </c>
       <c r="D11">
-        <v>388.0166807465542</v>
+        <v>387.7064025878058</v>
       </c>
       <c r="E11">
-        <v>-90.98599999999999</v>
+        <v>-86.73999999999999</v>
       </c>
       <c r="F11">
-        <v>38.214</v>
+        <v>42.45999999999999</v>
       </c>
       <c r="G11">
         <v>18</v>
@@ -2189,45 +2189,45 @@
         <v>21.483</v>
       </c>
       <c r="M11">
-        <v>1.9794852</v>
+        <v>2.271609999999999</v>
       </c>
       <c r="N11">
-        <v>19.5035148</v>
+        <v>19.21139</v>
       </c>
       <c r="O11">
-        <v>4.290773256</v>
+        <v>4.2265058</v>
       </c>
       <c r="P11">
-        <v>15.212741544</v>
+        <v>14.9848842</v>
       </c>
       <c r="Q11">
-        <v>16.129741544</v>
+        <v>15.9018842</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.06658928819448659</v>
+        <v>0.06677310152953951</v>
       </c>
       <c r="T11">
-        <v>0.4801221292029232</v>
+        <v>0.4843672408669632</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.22</v>
       </c>
       <c r="W11">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>10.85282173365075</v>
+        <v>9.457169144351365</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06426879137658556</v>
+        <v>0.06418563049618833</v>
       </c>
       <c r="C12">
-        <v>363.2464025878058</v>
+        <v>359.7143461213121</v>
       </c>
       <c r="D12">
-        <v>387.7064025878058</v>
+        <v>388.4203461213121</v>
       </c>
       <c r="E12">
-        <v>-86.73999999999998</v>
+        <v>-82.494</v>
       </c>
       <c r="F12">
-        <v>42.46</v>
+        <v>46.706</v>
       </c>
       <c r="G12">
         <v>18</v>
@@ -2271,28 +2271,28 @@
         <v>21.483</v>
       </c>
       <c r="M12">
-        <v>2.27161</v>
+        <v>2.498771</v>
       </c>
       <c r="N12">
-        <v>19.21139</v>
+        <v>18.984229</v>
       </c>
       <c r="O12">
-        <v>4.2265058</v>
+        <v>4.17653038</v>
       </c>
       <c r="P12">
-        <v>14.9848842</v>
+        <v>14.80769862</v>
       </c>
       <c r="Q12">
-        <v>15.9018842</v>
+        <v>15.72469862</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.06677310152953951</v>
+        <v>0.06696104550133521</v>
       </c>
       <c r="T12">
-        <v>0.4843672408669632</v>
+        <v>0.4887077482987345</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.457169144351363</v>
+        <v>8.597426494864877</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06418563049618833</v>
+        <v>0.06410246961579111</v>
       </c>
       <c r="C13">
-        <v>359.7143461213121</v>
+        <v>356.1849238941022</v>
       </c>
       <c r="D13">
-        <v>388.4203461213121</v>
+        <v>389.1369238941022</v>
       </c>
       <c r="E13">
-        <v>-82.494</v>
+        <v>-78.24799999999999</v>
       </c>
       <c r="F13">
-        <v>46.706</v>
+        <v>50.95199999999999</v>
       </c>
       <c r="G13">
         <v>18</v>
@@ -2353,28 +2353,28 @@
         <v>21.483</v>
       </c>
       <c r="M13">
-        <v>2.498771</v>
+        <v>2.725931999999999</v>
       </c>
       <c r="N13">
-        <v>18.984229</v>
+        <v>18.757068</v>
       </c>
       <c r="O13">
-        <v>4.17653038</v>
+        <v>4.126554959999999</v>
       </c>
       <c r="P13">
-        <v>14.80769862</v>
+        <v>14.63051304</v>
       </c>
       <c r="Q13">
-        <v>15.72469862</v>
+        <v>15.54751304</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.06696104550133521</v>
+        <v>0.06715326092703536</v>
       </c>
       <c r="T13">
-        <v>0.4887077482987345</v>
+        <v>0.4931469036266823</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.597426494864877</v>
+        <v>7.88097428695947</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06410246961579111</v>
+        <v>0.06410042873539389</v>
       </c>
       <c r="C14">
-        <v>356.1849238941022</v>
+        <v>351.9565429219699</v>
       </c>
       <c r="D14">
-        <v>389.1369238941022</v>
+        <v>389.1545429219699</v>
       </c>
       <c r="E14">
-        <v>-78.24799999999999</v>
+        <v>-74.00199999999998</v>
       </c>
       <c r="F14">
-        <v>50.95199999999999</v>
+        <v>55.198</v>
       </c>
       <c r="G14">
         <v>18</v>
@@ -2435,45 +2435,45 @@
         <v>21.483</v>
       </c>
       <c r="M14">
-        <v>2.725931999999999</v>
+        <v>2.9972514</v>
       </c>
       <c r="N14">
-        <v>18.757068</v>
+        <v>18.4857486</v>
       </c>
       <c r="O14">
-        <v>4.126554959999999</v>
+        <v>4.066864691999999</v>
       </c>
       <c r="P14">
-        <v>14.63051304</v>
+        <v>14.418883908</v>
       </c>
       <c r="Q14">
-        <v>15.54751304</v>
+        <v>15.335883908</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.06715326092703536</v>
+        <v>0.06734989509815389</v>
       </c>
       <c r="T14">
-        <v>0.4931469036266823</v>
+        <v>0.4976881085023991</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.22</v>
       </c>
       <c r="W14">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>7.88097428695947</v>
+        <v>7.167566924816516</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06410042873539389</v>
+        <v>0.06402350785499665</v>
       </c>
       <c r="C15">
-        <v>351.9565429219699</v>
+        <v>348.3757702072621</v>
       </c>
       <c r="D15">
-        <v>389.1545429219699</v>
+        <v>389.8197702072621</v>
       </c>
       <c r="E15">
-        <v>-74.00199999999998</v>
+        <v>-69.75599999999999</v>
       </c>
       <c r="F15">
-        <v>55.198</v>
+        <v>59.444</v>
       </c>
       <c r="G15">
         <v>18</v>
@@ -2517,28 +2517,28 @@
         <v>21.483</v>
       </c>
       <c r="M15">
-        <v>2.9972514</v>
+        <v>3.2278092</v>
       </c>
       <c r="N15">
-        <v>18.4857486</v>
+        <v>18.2551908</v>
       </c>
       <c r="O15">
-        <v>4.066864691999999</v>
+        <v>4.016141975999999</v>
       </c>
       <c r="P15">
-        <v>14.418883908</v>
+        <v>14.239048824</v>
       </c>
       <c r="Q15">
-        <v>15.335883908</v>
+        <v>15.156048824</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.06734989509815389</v>
+        <v>0.06755110215697285</v>
       </c>
       <c r="T15">
-        <v>0.4976881085023991</v>
+        <v>0.5023349227938302</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.167566924816516</v>
+        <v>6.655597858758193</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06402350785499665</v>
+        <v>0.06394658697459943</v>
       </c>
       <c r="C16">
-        <v>348.3757702072621</v>
+        <v>344.7972756882384</v>
       </c>
       <c r="D16">
-        <v>389.8197702072621</v>
+        <v>390.4872756882384</v>
       </c>
       <c r="E16">
-        <v>-69.75599999999999</v>
+        <v>-65.50999999999999</v>
       </c>
       <c r="F16">
-        <v>59.444</v>
+        <v>63.69</v>
       </c>
       <c r="G16">
         <v>18</v>
@@ -2599,28 +2599,28 @@
         <v>21.483</v>
       </c>
       <c r="M16">
-        <v>3.2278092</v>
+        <v>3.458367</v>
       </c>
       <c r="N16">
-        <v>18.2551908</v>
+        <v>18.024633</v>
       </c>
       <c r="O16">
-        <v>4.016141975999999</v>
+        <v>3.96541926</v>
       </c>
       <c r="P16">
-        <v>14.239048824</v>
+        <v>14.05921374</v>
       </c>
       <c r="Q16">
-        <v>15.156048824</v>
+        <v>14.97621374</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.06755110215697285</v>
+        <v>0.06775704349952874</v>
       </c>
       <c r="T16">
-        <v>0.5023349227938302</v>
+        <v>0.5070910738921185</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.655597858758193</v>
+        <v>6.21189133484098</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06394658697459943</v>
+        <v>0.0639944660942022</v>
       </c>
       <c r="C17">
-        <v>344.7972756882384</v>
+        <v>340.1355210255953</v>
       </c>
       <c r="D17">
-        <v>390.4872756882384</v>
+        <v>390.0715210255953</v>
       </c>
       <c r="E17">
-        <v>-65.50999999999999</v>
+        <v>-61.264</v>
       </c>
       <c r="F17">
-        <v>63.68999999999999</v>
+        <v>67.93599999999999</v>
       </c>
       <c r="G17">
         <v>18</v>
@@ -2681,45 +2681,45 @@
         <v>21.483</v>
       </c>
       <c r="M17">
-        <v>3.458367</v>
+        <v>3.7568608</v>
       </c>
       <c r="N17">
-        <v>18.024633</v>
+        <v>17.7261392</v>
       </c>
       <c r="O17">
-        <v>3.96541926</v>
+        <v>3.899750624</v>
       </c>
       <c r="P17">
-        <v>14.05921374</v>
+        <v>13.826388576</v>
       </c>
       <c r="Q17">
-        <v>14.97621374</v>
+        <v>14.743388576</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.06775704349952874</v>
+        <v>0.06796788820738357</v>
       </c>
       <c r="T17">
-        <v>0.5070910738921185</v>
+        <v>0.5119604666832231</v>
       </c>
       <c r="U17">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.22</v>
       </c>
       <c r="W17">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.211891334840981</v>
+        <v>5.71833803371155</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0639944660942022</v>
+        <v>0.06392534521380497</v>
       </c>
       <c r="C18">
-        <v>340.1355210255953</v>
+        <v>336.4900108394732</v>
       </c>
       <c r="D18">
-        <v>390.0715210255953</v>
+        <v>390.6720108394732</v>
       </c>
       <c r="E18">
-        <v>-61.264</v>
+        <v>-57.01799999999999</v>
       </c>
       <c r="F18">
-        <v>67.93599999999999</v>
+        <v>72.182</v>
       </c>
       <c r="G18">
         <v>18</v>
@@ -2763,28 +2763,28 @@
         <v>21.483</v>
       </c>
       <c r="M18">
-        <v>3.7568608</v>
+        <v>3.9916646</v>
       </c>
       <c r="N18">
-        <v>17.7261392</v>
+        <v>17.4913354</v>
       </c>
       <c r="O18">
-        <v>3.899750624</v>
+        <v>3.848093787999999</v>
       </c>
       <c r="P18">
-        <v>13.826388576</v>
+        <v>13.643241612</v>
       </c>
       <c r="Q18">
-        <v>14.743388576</v>
+        <v>14.560241612</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.06796788820738357</v>
+        <v>0.0681838135106084</v>
       </c>
       <c r="T18">
-        <v>0.5119604666832231</v>
+        <v>0.5169471942403786</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.71833803371155</v>
+        <v>5.381965208199104</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06392534521380497</v>
+        <v>0.06385622433340775</v>
       </c>
       <c r="C19">
-        <v>336.4900108394732</v>
+        <v>332.8463523341574</v>
       </c>
       <c r="D19">
-        <v>390.6720108394732</v>
+        <v>391.2743523341574</v>
       </c>
       <c r="E19">
-        <v>-57.01799999999999</v>
+        <v>-52.77199999999999</v>
       </c>
       <c r="F19">
-        <v>72.182</v>
+        <v>76.428</v>
       </c>
       <c r="G19">
         <v>18</v>
@@ -2845,28 +2845,28 @@
         <v>21.483</v>
       </c>
       <c r="M19">
-        <v>3.9916646</v>
+        <v>4.2264684</v>
       </c>
       <c r="N19">
-        <v>17.4913354</v>
+        <v>17.2565316</v>
       </c>
       <c r="O19">
-        <v>3.848093787999999</v>
+        <v>3.796436951999999</v>
       </c>
       <c r="P19">
-        <v>13.643241612</v>
+        <v>13.460094648</v>
       </c>
       <c r="Q19">
-        <v>14.560241612</v>
+        <v>14.377094648</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0681838135106084</v>
+        <v>0.06840500528464359</v>
       </c>
       <c r="T19">
-        <v>0.5169471942403786</v>
+        <v>0.5220555492989281</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.381965208199104</v>
+        <v>5.082967141076932</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06385622433340775</v>
+        <v>0.06378710345301053</v>
       </c>
       <c r="C20">
-        <v>332.8463523341574</v>
+        <v>329.2045540876862</v>
       </c>
       <c r="D20">
-        <v>391.2743523341574</v>
+        <v>391.8785540876862</v>
       </c>
       <c r="E20">
-        <v>-52.77199999999999</v>
+        <v>-48.526</v>
       </c>
       <c r="F20">
-        <v>76.428</v>
+        <v>80.67399999999999</v>
       </c>
       <c r="G20">
         <v>18</v>
@@ -2927,28 +2927,28 @@
         <v>21.483</v>
       </c>
       <c r="M20">
-        <v>4.2264684</v>
+        <v>4.4612722</v>
       </c>
       <c r="N20">
-        <v>17.2565316</v>
+        <v>17.0217278</v>
       </c>
       <c r="O20">
-        <v>3.796436951999999</v>
+        <v>3.744780115999999</v>
       </c>
       <c r="P20">
-        <v>13.460094648</v>
+        <v>13.276947684</v>
       </c>
       <c r="Q20">
-        <v>14.377094648</v>
+        <v>14.193947684</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.06840500528464359</v>
+        <v>0.0686316585839636</v>
       </c>
       <c r="T20">
-        <v>0.5220555492989281</v>
+        <v>0.5272900365811454</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.082967141076932</v>
+        <v>4.815442554704463</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06378710345301053</v>
+        <v>0.0637179825726133</v>
       </c>
       <c r="C21">
-        <v>329.2045540876862</v>
+        <v>325.5646247311645</v>
       </c>
       <c r="D21">
-        <v>391.8785540876862</v>
+        <v>392.4846247311645</v>
       </c>
       <c r="E21">
-        <v>-48.526</v>
+        <v>-44.27999999999999</v>
       </c>
       <c r="F21">
-        <v>80.67399999999999</v>
+        <v>84.92</v>
       </c>
       <c r="G21">
         <v>18</v>
@@ -3009,28 +3009,28 @@
         <v>21.483</v>
       </c>
       <c r="M21">
-        <v>4.4612722</v>
+        <v>4.696076000000001</v>
       </c>
       <c r="N21">
-        <v>17.0217278</v>
+        <v>16.786924</v>
       </c>
       <c r="O21">
-        <v>3.744780115999999</v>
+        <v>3.693123279999999</v>
       </c>
       <c r="P21">
-        <v>13.276947684</v>
+        <v>13.09380072</v>
       </c>
       <c r="Q21">
-        <v>14.193947684</v>
+        <v>14.01080072</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0686316585839636</v>
+        <v>0.06886397821576662</v>
       </c>
       <c r="T21">
-        <v>0.5272900365811454</v>
+        <v>0.5326553860454182</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.815442554704463</v>
+        <v>4.574670426969238</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0637179825726133</v>
+        <v>0.06405836169221607</v>
       </c>
       <c r="C22">
-        <v>325.5646247311645</v>
+        <v>318.3520656248264</v>
       </c>
       <c r="D22">
-        <v>392.4846247311645</v>
+        <v>389.5180656248264</v>
       </c>
       <c r="E22">
-        <v>-44.27999999999999</v>
+        <v>-40.03399999999999</v>
       </c>
       <c r="F22">
-        <v>84.92</v>
+        <v>89.166</v>
       </c>
       <c r="G22">
         <v>18</v>
@@ -3091,45 +3091,45 @@
         <v>21.483</v>
       </c>
       <c r="M22">
-        <v>4.696076000000001</v>
+        <v>5.1537948</v>
       </c>
       <c r="N22">
-        <v>16.786924</v>
+        <v>16.3292052</v>
       </c>
       <c r="O22">
-        <v>3.693123279999999</v>
+        <v>3.592425143999999</v>
       </c>
       <c r="P22">
-        <v>13.09380072</v>
+        <v>12.736780056</v>
       </c>
       <c r="Q22">
-        <v>14.01080072</v>
+        <v>13.653780056</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.06886397821576662</v>
+        <v>0.06910217935723553</v>
       </c>
       <c r="T22">
-        <v>0.5326553860454182</v>
+        <v>0.5381565671416979</v>
       </c>
       <c r="U22">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V22">
         <v>0.22</v>
       </c>
       <c r="W22">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.574670426969238</v>
+        <v>4.168384818114993</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06405836169221607</v>
+        <v>0.06460934081181884</v>
       </c>
       <c r="C23">
-        <v>318.3520656248264</v>
+        <v>309.3979311440643</v>
       </c>
       <c r="D23">
-        <v>389.5180656248264</v>
+        <v>384.8099311440643</v>
       </c>
       <c r="E23">
-        <v>-40.03400000000001</v>
+        <v>-35.788</v>
       </c>
       <c r="F23">
-        <v>89.16599999999998</v>
+        <v>93.41199999999999</v>
       </c>
       <c r="G23">
         <v>18</v>
@@ -3173,45 +3173,45 @@
         <v>21.483</v>
       </c>
       <c r="M23">
-        <v>5.153794799999999</v>
+        <v>5.726155599999999</v>
       </c>
       <c r="N23">
-        <v>16.3292052</v>
+        <v>15.7568444</v>
       </c>
       <c r="O23">
-        <v>3.592425143999999</v>
+        <v>3.466505768</v>
       </c>
       <c r="P23">
-        <v>12.736780056</v>
+        <v>12.290338632</v>
       </c>
       <c r="Q23">
-        <v>13.653780056</v>
+        <v>13.207338632</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.06910217935723552</v>
+        <v>0.06934648822028056</v>
       </c>
       <c r="T23">
-        <v>0.5381565671416978</v>
+        <v>0.5437988041635231</v>
       </c>
       <c r="U23">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V23">
         <v>0.22</v>
       </c>
       <c r="W23">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.168384818114994</v>
+        <v>3.751731790173498</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06460934081181884</v>
+        <v>0.06458701993142162</v>
       </c>
       <c r="C24">
-        <v>309.3979311440643</v>
+        <v>305.3404507034222</v>
       </c>
       <c r="D24">
-        <v>384.8099311440643</v>
+        <v>384.9984507034222</v>
       </c>
       <c r="E24">
-        <v>-35.788</v>
+        <v>-31.54199999999999</v>
       </c>
       <c r="F24">
-        <v>93.41199999999999</v>
+        <v>97.658</v>
       </c>
       <c r="G24">
         <v>18</v>
@@ -3255,28 +3255,28 @@
         <v>21.483</v>
       </c>
       <c r="M24">
-        <v>5.726155599999999</v>
+        <v>5.9864354</v>
       </c>
       <c r="N24">
-        <v>15.7568444</v>
+        <v>15.4965646</v>
       </c>
       <c r="O24">
-        <v>3.466505768</v>
+        <v>3.409244211999999</v>
       </c>
       <c r="P24">
-        <v>12.290338632</v>
+        <v>12.087320388</v>
       </c>
       <c r="Q24">
-        <v>13.207338632</v>
+        <v>13.004320388</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.06934648822028056</v>
+        <v>0.06959714276808002</v>
       </c>
       <c r="T24">
-        <v>0.5437988041635231</v>
+        <v>0.549587592796305</v>
       </c>
       <c r="U24">
         <v>0.0613</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.751731790173498</v>
+        <v>3.588613016687693</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06458701993142162</v>
+        <v>0.06508885905102438</v>
       </c>
       <c r="C25">
-        <v>305.3404507034222</v>
+        <v>296.9000979777234</v>
       </c>
       <c r="D25">
-        <v>384.9984507034222</v>
+        <v>380.8040979777234</v>
       </c>
       <c r="E25">
-        <v>-31.54199999999999</v>
+        <v>-27.29599999999999</v>
       </c>
       <c r="F25">
-        <v>97.658</v>
+        <v>101.904</v>
       </c>
       <c r="G25">
         <v>18</v>
@@ -3337,45 +3337,45 @@
         <v>21.483</v>
       </c>
       <c r="M25">
-        <v>5.9864354</v>
+        <v>6.5320464</v>
       </c>
       <c r="N25">
-        <v>15.4965646</v>
+        <v>14.9509536</v>
       </c>
       <c r="O25">
-        <v>3.409244211999999</v>
+        <v>3.289209791999999</v>
       </c>
       <c r="P25">
-        <v>12.087320388</v>
+        <v>11.661743808</v>
       </c>
       <c r="Q25">
-        <v>13.004320388</v>
+        <v>12.578743808</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.06959714276808002</v>
+        <v>0.06985439348818998</v>
       </c>
       <c r="T25">
-        <v>0.549587592796305</v>
+        <v>0.5555287179720547</v>
       </c>
       <c r="U25">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V25">
         <v>0.22</v>
       </c>
       <c r="W25">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.588613016687693</v>
+        <v>3.288862124433163</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06508885905102438</v>
+        <v>0.06508837817062715</v>
       </c>
       <c r="C26">
-        <v>296.9000979777234</v>
+        <v>292.6580734128999</v>
       </c>
       <c r="D26">
-        <v>380.8040979777234</v>
+        <v>380.8080734128998</v>
       </c>
       <c r="E26">
-        <v>-27.29600000000001</v>
+        <v>-23.05</v>
       </c>
       <c r="F26">
-        <v>101.904</v>
+        <v>106.15</v>
       </c>
       <c r="G26">
         <v>18</v>
@@ -3419,28 +3419,28 @@
         <v>21.483</v>
       </c>
       <c r="M26">
-        <v>6.5320464</v>
+        <v>6.804215</v>
       </c>
       <c r="N26">
-        <v>14.9509536</v>
+        <v>14.678785</v>
       </c>
       <c r="O26">
-        <v>3.289209792</v>
+        <v>3.2293327</v>
       </c>
       <c r="P26">
-        <v>11.661743808</v>
+        <v>11.4494523</v>
       </c>
       <c r="Q26">
-        <v>12.578743808</v>
+        <v>12.3664523</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.06985439348818998</v>
+        <v>0.07011850422750288</v>
       </c>
       <c r="T26">
-        <v>0.5555287179720547</v>
+        <v>0.5616282731524911</v>
       </c>
       <c r="U26">
         <v>0.0641</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.288862124433164</v>
+        <v>3.157307639455837</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06508837817062715</v>
+        <v>0.06508789729022993</v>
       </c>
       <c r="C27">
-        <v>292.6580734128999</v>
+        <v>288.4160489310809</v>
       </c>
       <c r="D27">
-        <v>380.8080734128998</v>
+        <v>380.8120489310809</v>
       </c>
       <c r="E27">
-        <v>-23.05</v>
+        <v>-18.80399999999999</v>
       </c>
       <c r="F27">
-        <v>106.15</v>
+        <v>110.396</v>
       </c>
       <c r="G27">
         <v>18</v>
@@ -3501,28 +3501,28 @@
         <v>21.483</v>
       </c>
       <c r="M27">
-        <v>6.804215</v>
+        <v>7.076383600000001</v>
       </c>
       <c r="N27">
-        <v>14.678785</v>
+        <v>14.4066164</v>
       </c>
       <c r="O27">
-        <v>3.2293327</v>
+        <v>3.169455607999999</v>
       </c>
       <c r="P27">
-        <v>11.4494523</v>
+        <v>11.237160792</v>
       </c>
       <c r="Q27">
-        <v>12.3664523</v>
+        <v>12.154160792</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07011850422750288</v>
+        <v>0.07038975309490531</v>
       </c>
       <c r="T27">
-        <v>0.5616282731524911</v>
+        <v>0.5678926811756421</v>
       </c>
       <c r="U27">
         <v>0.0641</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.157307639455837</v>
+        <v>3.035872730245997</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06508789729022993</v>
+        <v>0.0667300964098327</v>
       </c>
       <c r="C28">
-        <v>288.4160489310809</v>
+        <v>271.0609321869766</v>
       </c>
       <c r="D28">
-        <v>380.8120489310809</v>
+        <v>367.7029321869766</v>
       </c>
       <c r="E28">
-        <v>-18.80399999999999</v>
+        <v>-14.55799999999999</v>
       </c>
       <c r="F28">
-        <v>110.396</v>
+        <v>114.642</v>
       </c>
       <c r="G28">
         <v>18</v>
@@ -3583,45 +3583,45 @@
         <v>21.483</v>
       </c>
       <c r="M28">
-        <v>7.076383600000001</v>
+        <v>8.2427598</v>
       </c>
       <c r="N28">
-        <v>14.4066164</v>
+        <v>13.2402402</v>
       </c>
       <c r="O28">
-        <v>3.169455607999999</v>
+        <v>2.912852843999999</v>
       </c>
       <c r="P28">
-        <v>11.237160792</v>
+        <v>10.327387356</v>
       </c>
       <c r="Q28">
-        <v>12.154160792</v>
+        <v>11.244387356</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07038975309490531</v>
+        <v>0.07066843343812698</v>
       </c>
       <c r="T28">
-        <v>0.5678926811756421</v>
+        <v>0.5743287168158655</v>
       </c>
       <c r="U28">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V28">
         <v>0.22</v>
       </c>
       <c r="W28">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.035872730245997</v>
+        <v>2.606287277714922</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0667300964098327</v>
+        <v>0.06679045552943547</v>
       </c>
       <c r="C29">
-        <v>271.0609321869766</v>
+        <v>266.3502802236286</v>
       </c>
       <c r="D29">
-        <v>367.7029321869766</v>
+        <v>367.2382802236286</v>
       </c>
       <c r="E29">
-        <v>-14.55799999999999</v>
+        <v>-10.31199999999998</v>
       </c>
       <c r="F29">
-        <v>114.642</v>
+        <v>118.888</v>
       </c>
       <c r="G29">
         <v>18</v>
@@ -3665,28 +3665,28 @@
         <v>21.483</v>
       </c>
       <c r="M29">
-        <v>8.2427598</v>
+        <v>8.548047200000001</v>
       </c>
       <c r="N29">
-        <v>13.2402402</v>
+        <v>12.9349528</v>
       </c>
       <c r="O29">
-        <v>2.912852843999999</v>
+        <v>2.845689615999999</v>
       </c>
       <c r="P29">
-        <v>10.327387356</v>
+        <v>10.089263184</v>
       </c>
       <c r="Q29">
-        <v>11.244387356</v>
+        <v>11.006263184</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07066843343812698</v>
+        <v>0.07095485490199371</v>
       </c>
       <c r="T29">
-        <v>0.5743287168158655</v>
+        <v>0.5809435312238731</v>
       </c>
       <c r="U29">
         <v>0.07190000000000001</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.606287277714922</v>
+        <v>2.513205589225104</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06679045552943547</v>
+        <v>0.06773299464903824</v>
       </c>
       <c r="C30">
-        <v>266.3502802236286</v>
+        <v>254.9978948145891</v>
       </c>
       <c r="D30">
-        <v>367.2382802236286</v>
+        <v>360.1318948145891</v>
       </c>
       <c r="E30">
-        <v>-10.31199999999998</v>
+        <v>-6.065999999999988</v>
       </c>
       <c r="F30">
-        <v>118.888</v>
+        <v>123.134</v>
       </c>
       <c r="G30">
         <v>18</v>
@@ -3747,45 +3747,45 @@
         <v>21.483</v>
       </c>
       <c r="M30">
-        <v>8.548047200000001</v>
+        <v>9.333557200000001</v>
       </c>
       <c r="N30">
-        <v>12.9349528</v>
+        <v>12.1494428</v>
       </c>
       <c r="O30">
-        <v>2.845689615999999</v>
+        <v>2.672877415999999</v>
       </c>
       <c r="P30">
-        <v>10.089263184</v>
+        <v>9.476565383999997</v>
       </c>
       <c r="Q30">
-        <v>11.006263184</v>
+        <v>10.393565384</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07095485490199371</v>
+        <v>0.07124934457611021</v>
       </c>
       <c r="T30">
-        <v>0.5809435312238731</v>
+        <v>0.5877446784321062</v>
       </c>
       <c r="U30">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V30">
         <v>0.22</v>
       </c>
       <c r="W30">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.513205589225104</v>
+        <v>2.301694792206341</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06773299464903824</v>
+        <v>0.06782377376864102</v>
       </c>
       <c r="C31">
-        <v>254.9978948145891</v>
+        <v>250.0819480129416</v>
       </c>
       <c r="D31">
-        <v>360.1318948145891</v>
+        <v>359.4619480129416</v>
       </c>
       <c r="E31">
-        <v>-6.066000000000003</v>
+        <v>-1.820000000000007</v>
       </c>
       <c r="F31">
-        <v>123.134</v>
+        <v>127.38</v>
       </c>
       <c r="G31">
         <v>18</v>
@@ -3829,28 +3829,28 @@
         <v>21.483</v>
       </c>
       <c r="M31">
-        <v>9.3335572</v>
+        <v>9.655403999999999</v>
       </c>
       <c r="N31">
-        <v>12.1494428</v>
+        <v>11.827596</v>
       </c>
       <c r="O31">
-        <v>2.672877416</v>
+        <v>2.60207112</v>
       </c>
       <c r="P31">
-        <v>9.476565383999997</v>
+        <v>9.225524879999998</v>
       </c>
       <c r="Q31">
-        <v>10.393565384</v>
+        <v>10.14252488</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07124934457611021</v>
+        <v>0.07155224824091574</v>
       </c>
       <c r="T31">
-        <v>0.5877446784321062</v>
+        <v>0.594740144132003</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.301694792206341</v>
+        <v>2.22497163246613</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06782377376864102</v>
+        <v>0.0679145528882438</v>
       </c>
       <c r="C32">
-        <v>250.0819480129416</v>
+        <v>245.1684891626583</v>
       </c>
       <c r="D32">
-        <v>359.4619480129416</v>
+        <v>358.7944891626583</v>
       </c>
       <c r="E32">
-        <v>-1.820000000000007</v>
+        <v>2.425999999999988</v>
       </c>
       <c r="F32">
-        <v>127.38</v>
+        <v>131.626</v>
       </c>
       <c r="G32">
         <v>18</v>
@@ -3911,28 +3911,28 @@
         <v>21.483</v>
       </c>
       <c r="M32">
-        <v>9.655403999999999</v>
+        <v>9.977250799999998</v>
       </c>
       <c r="N32">
-        <v>11.827596</v>
+        <v>11.5057492</v>
       </c>
       <c r="O32">
-        <v>2.60207112</v>
+        <v>2.531264824</v>
       </c>
       <c r="P32">
-        <v>9.225524879999998</v>
+        <v>8.974484375999999</v>
       </c>
       <c r="Q32">
-        <v>10.14252488</v>
+        <v>9.891484375999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07155224824091574</v>
+        <v>0.07186393172209246</v>
       </c>
       <c r="T32">
-        <v>0.594740144132003</v>
+        <v>0.6019383769536362</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.22497163246613</v>
+        <v>2.153198353999481</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0679145528882438</v>
+        <v>0.06800533200784656</v>
       </c>
       <c r="C33">
-        <v>245.1684891626583</v>
+        <v>240.2575044303357</v>
       </c>
       <c r="D33">
-        <v>358.7944891626583</v>
+        <v>358.1295044303357</v>
       </c>
       <c r="E33">
-        <v>2.425999999999988</v>
+        <v>6.671999999999997</v>
       </c>
       <c r="F33">
-        <v>131.626</v>
+        <v>135.872</v>
       </c>
       <c r="G33">
         <v>18</v>
@@ -3993,28 +3993,28 @@
         <v>21.483</v>
       </c>
       <c r="M33">
-        <v>9.977250799999998</v>
+        <v>10.2990976</v>
       </c>
       <c r="N33">
-        <v>11.5057492</v>
+        <v>11.1839024</v>
       </c>
       <c r="O33">
-        <v>2.531264824</v>
+        <v>2.460458527999999</v>
       </c>
       <c r="P33">
-        <v>8.974484375999999</v>
+        <v>8.723443871999997</v>
       </c>
       <c r="Q33">
-        <v>9.891484375999999</v>
+        <v>9.640443871999997</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07186393172209246</v>
+        <v>0.07218478236448024</v>
       </c>
       <c r="T33">
-        <v>0.6019383769536362</v>
+        <v>0.6093483225053172</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.153198353999481</v>
+        <v>2.085910905436997</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06800533200784656</v>
+        <v>0.06809611112744933</v>
       </c>
       <c r="C34">
-        <v>240.2575044303357</v>
+        <v>235.3489800849348</v>
       </c>
       <c r="D34">
-        <v>358.1295044303357</v>
+        <v>357.4669800849348</v>
       </c>
       <c r="E34">
-        <v>6.671999999999997</v>
+        <v>10.91800000000001</v>
       </c>
       <c r="F34">
-        <v>135.872</v>
+        <v>140.118</v>
       </c>
       <c r="G34">
         <v>18</v>
@@ -4075,28 +4075,28 @@
         <v>21.483</v>
       </c>
       <c r="M34">
-        <v>10.2990976</v>
+        <v>10.6209444</v>
       </c>
       <c r="N34">
-        <v>11.1839024</v>
+        <v>10.8620556</v>
       </c>
       <c r="O34">
-        <v>2.460458527999999</v>
+        <v>2.389652231999999</v>
       </c>
       <c r="P34">
-        <v>8.723443871999997</v>
+        <v>8.472403367999997</v>
       </c>
       <c r="Q34">
-        <v>9.640443871999997</v>
+        <v>9.389403367999996</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07218478236448024</v>
+        <v>0.07251521063798408</v>
       </c>
       <c r="T34">
-        <v>0.6093483225053172</v>
+        <v>0.616979460461526</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.085910905436997</v>
+        <v>2.022701484060118</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06809611112744933</v>
+        <v>0.07195273024705209</v>
       </c>
       <c r="C35">
-        <v>235.3489800849348</v>
+        <v>205.05578545412</v>
       </c>
       <c r="D35">
-        <v>357.4669800849348</v>
+        <v>331.41978545412</v>
       </c>
       <c r="E35">
-        <v>10.91800000000001</v>
+        <v>15.16400000000002</v>
       </c>
       <c r="F35">
-        <v>140.118</v>
+        <v>144.364</v>
       </c>
       <c r="G35">
         <v>18</v>
@@ -4157,45 +4157,45 @@
         <v>21.483</v>
       </c>
       <c r="M35">
-        <v>10.6209444</v>
+        <v>12.99276</v>
       </c>
       <c r="N35">
-        <v>10.8620556</v>
+        <v>8.490239999999996</v>
       </c>
       <c r="O35">
-        <v>2.389652231999999</v>
+        <v>1.867852799999999</v>
       </c>
       <c r="P35">
-        <v>8.472403367999997</v>
+        <v>6.622387199999997</v>
       </c>
       <c r="Q35">
-        <v>9.389403367999996</v>
+        <v>7.539387199999997</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07251521063798408</v>
+        <v>0.07285565188947289</v>
       </c>
       <c r="T35">
-        <v>0.616979460461526</v>
+        <v>0.6248418450224684</v>
       </c>
       <c r="U35">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V35">
         <v>0.22</v>
       </c>
       <c r="W35">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.022701484060118</v>
+        <v>1.653459311185614</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07195273024705209</v>
+        <v>0.07215426936665488</v>
       </c>
       <c r="C36">
-        <v>205.05578545412</v>
+        <v>199.5525822376374</v>
       </c>
       <c r="D36">
-        <v>331.41978545412</v>
+        <v>330.1625822376374</v>
       </c>
       <c r="E36">
-        <v>15.16400000000002</v>
+        <v>19.41000000000003</v>
       </c>
       <c r="F36">
-        <v>144.364</v>
+        <v>148.61</v>
       </c>
       <c r="G36">
         <v>18</v>
@@ -4239,28 +4239,28 @@
         <v>21.483</v>
       </c>
       <c r="M36">
-        <v>12.99276</v>
+        <v>13.3749</v>
       </c>
       <c r="N36">
-        <v>8.490239999999996</v>
+        <v>8.108099999999997</v>
       </c>
       <c r="O36">
-        <v>1.867852799999999</v>
+        <v>1.783781999999999</v>
       </c>
       <c r="P36">
-        <v>6.622387199999997</v>
+        <v>6.324317999999997</v>
       </c>
       <c r="Q36">
-        <v>7.539387199999997</v>
+        <v>7.241317999999997</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07285565188947289</v>
+        <v>0.07320656825639213</v>
       </c>
       <c r="T36">
-        <v>0.6248418450224684</v>
+        <v>0.632946149108363</v>
       </c>
       <c r="U36">
         <v>0.09</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>1.653459311185614</v>
+        <v>1.606217616580311</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07215426936665488</v>
+        <v>0.07235580848625767</v>
       </c>
       <c r="C37">
-        <v>199.5525822376374</v>
+        <v>194.0588810906177</v>
       </c>
       <c r="D37">
-        <v>330.1625822376374</v>
+        <v>328.9148810906177</v>
       </c>
       <c r="E37">
-        <v>19.41000000000003</v>
+        <v>23.65600000000001</v>
       </c>
       <c r="F37">
-        <v>148.61</v>
+        <v>152.856</v>
       </c>
       <c r="G37">
         <v>18</v>
@@ -4321,28 +4321,28 @@
         <v>21.483</v>
       </c>
       <c r="M37">
-        <v>13.3749</v>
+        <v>13.75704</v>
       </c>
       <c r="N37">
-        <v>8.108099999999997</v>
+        <v>7.725959999999999</v>
       </c>
       <c r="O37">
-        <v>1.783781999999999</v>
+        <v>1.6997112</v>
       </c>
       <c r="P37">
-        <v>6.324317999999997</v>
+        <v>6.026248799999999</v>
       </c>
       <c r="Q37">
-        <v>7.241317999999997</v>
+        <v>6.943248799999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07320656825639213</v>
+        <v>0.0735684507597776</v>
       </c>
       <c r="T37">
-        <v>0.632946149108363</v>
+        <v>0.6413037126969419</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.606217616580311</v>
+        <v>1.561600460564191</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07235580848625765</v>
+        <v>0.07255734760586043</v>
       </c>
       <c r="C38">
-        <v>194.0588810906178</v>
+        <v>188.5745746922244</v>
       </c>
       <c r="D38">
-        <v>328.9148810906178</v>
+        <v>327.6765746922243</v>
       </c>
       <c r="E38">
-        <v>23.65600000000001</v>
+        <v>27.90199999999999</v>
       </c>
       <c r="F38">
-        <v>152.856</v>
+        <v>157.102</v>
       </c>
       <c r="G38">
         <v>18</v>
@@ -4403,28 +4403,28 @@
         <v>21.483</v>
       </c>
       <c r="M38">
-        <v>13.75704</v>
+        <v>14.13918</v>
       </c>
       <c r="N38">
-        <v>7.725959999999999</v>
+        <v>7.343819999999999</v>
       </c>
       <c r="O38">
-        <v>1.6997112</v>
+        <v>1.6156404</v>
       </c>
       <c r="P38">
-        <v>6.026248799999999</v>
+        <v>5.728179599999999</v>
       </c>
       <c r="Q38">
-        <v>6.943248799999999</v>
+        <v>6.645179599999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07356845075977758</v>
+        <v>0.07394182159660385</v>
       </c>
       <c r="T38">
-        <v>0.6413037126969418</v>
+        <v>0.6499265957645229</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.561600460564191</v>
+        <v>1.519395042711105</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07255734760586043</v>
+        <v>0.09088586213549663</v>
       </c>
       <c r="C39">
-        <v>188.5745746922244</v>
+        <v>100.7526140426521</v>
       </c>
       <c r="D39">
-        <v>327.6765746922243</v>
+        <v>244.1006140426521</v>
       </c>
       <c r="E39">
-        <v>27.90199999999999</v>
+        <v>32.148</v>
       </c>
       <c r="F39">
-        <v>157.102</v>
+        <v>161.348</v>
       </c>
       <c r="G39">
         <v>18</v>
@@ -4485,45 +4485,45 @@
         <v>21.483</v>
       </c>
       <c r="M39">
-        <v>14.13918</v>
+        <v>23.6858864</v>
       </c>
       <c r="N39">
-        <v>7.343819999999999</v>
+        <v>-2.202886400000004</v>
       </c>
       <c r="O39">
-        <v>1.6156404</v>
+        <v>-0.4846350080000009</v>
       </c>
       <c r="P39">
-        <v>5.728179599999999</v>
+        <v>-1.718251392000003</v>
       </c>
       <c r="Q39">
-        <v>6.645179599999999</v>
+        <v>-0.8012513920000031</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.07394182159660385</v>
+        <v>0.0745692745458035</v>
       </c>
       <c r="T39">
-        <v>0.6499265957645229</v>
+        <v>0.6644174260000808</v>
       </c>
       <c r="U39">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.22</v>
+        <v>0.1995390807920112</v>
       </c>
       <c r="W39">
-        <v>0.0702</v>
+        <v>0.1175076629397328</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y39">
-        <v>1.519395042711105</v>
+        <v>0.906995821781869</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09088586213549663</v>
+        <v>0.09189586213549662</v>
       </c>
       <c r="C40">
-        <v>100.7526140426521</v>
+        <v>93.12333779804845</v>
       </c>
       <c r="D40">
-        <v>244.1006140426521</v>
+        <v>240.7173377980485</v>
       </c>
       <c r="E40">
-        <v>32.148</v>
+        <v>36.39400000000001</v>
       </c>
       <c r="F40">
-        <v>161.348</v>
+        <v>165.594</v>
       </c>
       <c r="G40">
         <v>18</v>
@@ -4567,37 +4567,37 @@
         <v>21.483</v>
       </c>
       <c r="M40">
-        <v>23.6858864</v>
+        <v>24.3091992</v>
       </c>
       <c r="N40">
-        <v>-2.202886400000004</v>
+        <v>-2.826199200000005</v>
       </c>
       <c r="O40">
-        <v>-0.4846350080000009</v>
+        <v>-0.6217638240000011</v>
       </c>
       <c r="P40">
-        <v>-1.718251392000003</v>
+        <v>-2.204435376000004</v>
       </c>
       <c r="Q40">
-        <v>-0.8012513920000031</v>
+        <v>-1.287435376000004</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.0745692745458035</v>
+        <v>0.07504090199737405</v>
       </c>
       <c r="T40">
-        <v>0.6644174260000808</v>
+        <v>0.6753095149509017</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.1995390807920112</v>
+        <v>0.1944226941050365</v>
       </c>
       <c r="W40">
-        <v>0.1175076629397328</v>
+        <v>0.1182587485053807</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.906995821781869</v>
+        <v>0.883739518659257</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09189586213549662</v>
+        <v>0.09290586213549663</v>
       </c>
       <c r="C41">
-        <v>93.12333779804845</v>
+        <v>85.58656501404585</v>
       </c>
       <c r="D41">
-        <v>240.7173377980485</v>
+        <v>237.4265650140458</v>
       </c>
       <c r="E41">
-        <v>36.39400000000001</v>
+        <v>40.64000000000001</v>
       </c>
       <c r="F41">
-        <v>165.594</v>
+        <v>169.84</v>
       </c>
       <c r="G41">
         <v>18</v>
@@ -4649,37 +4649,37 @@
         <v>21.483</v>
       </c>
       <c r="M41">
-        <v>24.3091992</v>
+        <v>24.932512</v>
       </c>
       <c r="N41">
-        <v>-2.826199200000005</v>
+        <v>-3.449512000000006</v>
       </c>
       <c r="O41">
-        <v>-0.6217638240000011</v>
+        <v>-0.7588926400000012</v>
       </c>
       <c r="P41">
-        <v>-2.204435376000004</v>
+        <v>-2.690619360000004</v>
       </c>
       <c r="Q41">
-        <v>-1.287435376000004</v>
+        <v>-1.773619360000004</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.07504090199737405</v>
+        <v>0.07552825036399696</v>
       </c>
       <c r="T41">
-        <v>0.6753095149509017</v>
+        <v>0.6865646735334168</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.1944226941050365</v>
+        <v>0.1895621267524106</v>
       </c>
       <c r="W41">
-        <v>0.1182587485053807</v>
+        <v>0.1189722797927461</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.883739518659257</v>
+        <v>0.8616460306927756</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09290586213549663</v>
+        <v>0.09391586213549663</v>
       </c>
       <c r="C42">
-        <v>85.58656501404585</v>
+        <v>78.13855309532852</v>
       </c>
       <c r="D42">
-        <v>237.4265650140458</v>
+        <v>234.2245530953285</v>
       </c>
       <c r="E42">
-        <v>40.64000000000001</v>
+        <v>44.88600000000002</v>
       </c>
       <c r="F42">
-        <v>169.84</v>
+        <v>174.086</v>
       </c>
       <c r="G42">
         <v>18</v>
@@ -4731,37 +4731,37 @@
         <v>21.483</v>
       </c>
       <c r="M42">
-        <v>24.932512</v>
+        <v>25.5558248</v>
       </c>
       <c r="N42">
-        <v>-3.449512000000006</v>
+        <v>-4.072824800000006</v>
       </c>
       <c r="O42">
-        <v>-0.7588926400000012</v>
+        <v>-0.8960214560000014</v>
       </c>
       <c r="P42">
-        <v>-2.690619360000004</v>
+        <v>-3.176803344000005</v>
       </c>
       <c r="Q42">
-        <v>-1.773619360000004</v>
+        <v>-2.259803344000005</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.07552825036399696</v>
+        <v>0.07603211901423419</v>
       </c>
       <c r="T42">
-        <v>0.6865646735334168</v>
+        <v>0.6982013629153392</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.1895621267524106</v>
+        <v>0.1849386602462543</v>
       </c>
       <c r="W42">
-        <v>0.1189722797927461</v>
+        <v>0.1196510046758499</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8616460306927756</v>
+        <v>0.8406302738466103</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09391586213549663</v>
+        <v>0.09492586213549663</v>
       </c>
       <c r="C43">
-        <v>78.13855309532852</v>
+        <v>70.77575865541854</v>
       </c>
       <c r="D43">
-        <v>234.2245530953285</v>
+        <v>231.1077586554185</v>
       </c>
       <c r="E43">
-        <v>44.88600000000002</v>
+        <v>49.13200000000001</v>
       </c>
       <c r="F43">
-        <v>174.086</v>
+        <v>178.332</v>
       </c>
       <c r="G43">
         <v>18</v>
@@ -4813,37 +4813,37 @@
         <v>21.483</v>
       </c>
       <c r="M43">
-        <v>25.5558248</v>
+        <v>26.1791376</v>
       </c>
       <c r="N43">
-        <v>-4.072824800000006</v>
+        <v>-4.696137600000004</v>
       </c>
       <c r="O43">
-        <v>-0.8960214560000014</v>
+        <v>-1.033150272000001</v>
       </c>
       <c r="P43">
-        <v>-3.176803344000005</v>
+        <v>-3.662987328000003</v>
       </c>
       <c r="Q43">
-        <v>-2.259803344000005</v>
+        <v>-2.745987328000003</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.07603211901423419</v>
+        <v>0.0765533624455141</v>
       </c>
       <c r="T43">
-        <v>0.6982013629153392</v>
+        <v>0.7102393174483623</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.1849386602462543</v>
+        <v>0.1805353588118196</v>
       </c>
       <c r="W43">
-        <v>0.1196510046758499</v>
+        <v>0.1202974093264249</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8406302738466103</v>
+        <v>0.820615267326453</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09492586213549663</v>
+        <v>0.09593586213549664</v>
       </c>
       <c r="C44">
-        <v>70.77575865541857</v>
+        <v>63.49482443650703</v>
       </c>
       <c r="D44">
-        <v>231.1077586554185</v>
+        <v>228.072824436507</v>
       </c>
       <c r="E44">
-        <v>49.13199999999998</v>
+        <v>53.37799999999999</v>
       </c>
       <c r="F44">
-        <v>178.332</v>
+        <v>182.578</v>
       </c>
       <c r="G44">
         <v>18</v>
@@ -4895,37 +4895,37 @@
         <v>21.483</v>
       </c>
       <c r="M44">
-        <v>26.1791376</v>
+        <v>26.8024504</v>
       </c>
       <c r="N44">
-        <v>-4.6961376</v>
+        <v>-5.319450400000001</v>
       </c>
       <c r="O44">
-        <v>-1.033150272</v>
+        <v>-1.170279088</v>
       </c>
       <c r="P44">
-        <v>-3.662987328</v>
+        <v>-4.149171312000001</v>
       </c>
       <c r="Q44">
-        <v>-2.745987328</v>
+        <v>-3.232171312000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.07655336244551408</v>
+        <v>0.0770928951199968</v>
       </c>
       <c r="T44">
-        <v>0.7102393174483621</v>
+        <v>0.7226996563509651</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.1805353588118197</v>
+        <v>0.1763368620952657</v>
       </c>
       <c r="W44">
-        <v>0.1202974093264249</v>
+        <v>0.120913748644415</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8206152673264531</v>
+        <v>0.8015311913421169</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09593586213549664</v>
+        <v>0.1210994193962368</v>
       </c>
       <c r="C45">
-        <v>63.49482443650703</v>
+        <v>3.023825159735651</v>
       </c>
       <c r="D45">
-        <v>228.072824436507</v>
+        <v>171.8478251597356</v>
       </c>
       <c r="E45">
-        <v>53.37799999999999</v>
+        <v>57.624</v>
       </c>
       <c r="F45">
-        <v>182.578</v>
+        <v>186.824</v>
       </c>
       <c r="G45">
         <v>18</v>
@@ -4977,45 +4977,45 @@
         <v>21.483</v>
       </c>
       <c r="M45">
-        <v>26.8024504</v>
+        <v>37.5142592</v>
       </c>
       <c r="N45">
-        <v>-5.319450400000001</v>
+        <v>-16.0312592</v>
       </c>
       <c r="O45">
-        <v>-1.170279088</v>
+        <v>-3.526877024</v>
       </c>
       <c r="P45">
-        <v>-4.149171312000001</v>
+        <v>-12.504382176</v>
       </c>
       <c r="Q45">
-        <v>-3.232171312000001</v>
+        <v>-11.587382176</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.0770928951199968</v>
+        <v>0.07835447764131842</v>
       </c>
       <c r="T45">
-        <v>0.7226996563509651</v>
+        <v>0.7518355113468457</v>
       </c>
       <c r="U45">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1763368620952657</v>
+        <v>0.1259856945275891</v>
       </c>
       <c r="W45">
-        <v>0.120913748644415</v>
+        <v>0.1755020725388601</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.8015311913421169</v>
+        <v>0.5726622478526777</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1210994193962368</v>
+        <v>0.1226494193962368</v>
       </c>
       <c r="C46">
-        <v>3.023825159735651</v>
+        <v>-3.792655950954298</v>
       </c>
       <c r="D46">
-        <v>171.8478251597356</v>
+        <v>169.2773440490457</v>
       </c>
       <c r="E46">
-        <v>57.624</v>
+        <v>61.87</v>
       </c>
       <c r="F46">
-        <v>186.824</v>
+        <v>191.07</v>
       </c>
       <c r="G46">
         <v>18</v>
@@ -5059,37 +5059,37 @@
         <v>21.483</v>
       </c>
       <c r="M46">
-        <v>37.5142592</v>
+        <v>38.366856</v>
       </c>
       <c r="N46">
-        <v>-16.0312592</v>
+        <v>-16.883856</v>
       </c>
       <c r="O46">
-        <v>-3.526877024</v>
+        <v>-3.71444832</v>
       </c>
       <c r="P46">
-        <v>-12.504382176</v>
+        <v>-13.16940768</v>
       </c>
       <c r="Q46">
-        <v>-11.587382176</v>
+        <v>-12.25240768</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.07835447764131842</v>
+        <v>0.07894637723479694</v>
       </c>
       <c r="T46">
-        <v>0.7518355113468457</v>
+        <v>0.7655052479167883</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1259856945275891</v>
+        <v>0.123186012426976</v>
       </c>
       <c r="W46">
-        <v>0.1755020725388601</v>
+        <v>0.1760642487046632</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5726622478526777</v>
+        <v>0.5599364201226182</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1226494193962368</v>
+        <v>0.1241994193962368</v>
       </c>
       <c r="C47">
-        <v>-3.792655950954298</v>
+        <v>-10.53337238668897</v>
       </c>
       <c r="D47">
-        <v>169.2773440490457</v>
+        <v>166.782627613311</v>
       </c>
       <c r="E47">
-        <v>61.87</v>
+        <v>66.11600000000001</v>
       </c>
       <c r="F47">
-        <v>191.07</v>
+        <v>195.316</v>
       </c>
       <c r="G47">
         <v>18</v>
@@ -5141,37 +5141,37 @@
         <v>21.483</v>
       </c>
       <c r="M47">
-        <v>38.366856</v>
+        <v>39.2194528</v>
       </c>
       <c r="N47">
-        <v>-16.883856</v>
+        <v>-17.7364528</v>
       </c>
       <c r="O47">
-        <v>-3.71444832</v>
+        <v>-3.902019616</v>
       </c>
       <c r="P47">
-        <v>-13.16940768</v>
+        <v>-13.834433184</v>
       </c>
       <c r="Q47">
-        <v>-12.25240768</v>
+        <v>-12.917433184</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.07894637723479694</v>
+        <v>0.07956019903544134</v>
       </c>
       <c r="T47">
-        <v>0.7655052479167883</v>
+        <v>0.7796812710263586</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.123186012426976</v>
+        <v>0.1205080556350852</v>
       </c>
       <c r="W47">
-        <v>0.1760642487046632</v>
+        <v>0.1766019824284749</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5599364201226182</v>
+        <v>0.5477638892503874</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1241994193962368</v>
+        <v>0.1257494193962368</v>
       </c>
       <c r="C48">
-        <v>-10.53337238668897</v>
+        <v>-17.20162523227788</v>
       </c>
       <c r="D48">
-        <v>166.782627613311</v>
+        <v>164.3603747677221</v>
       </c>
       <c r="E48">
-        <v>66.11600000000001</v>
+        <v>70.36199999999999</v>
       </c>
       <c r="F48">
-        <v>195.316</v>
+        <v>199.562</v>
       </c>
       <c r="G48">
         <v>18</v>
@@ -5223,37 +5223,37 @@
         <v>21.483</v>
       </c>
       <c r="M48">
-        <v>39.2194528</v>
+        <v>40.0720496</v>
       </c>
       <c r="N48">
-        <v>-17.7364528</v>
+        <v>-18.5890496</v>
       </c>
       <c r="O48">
-        <v>-3.902019616</v>
+        <v>-4.089590912</v>
       </c>
       <c r="P48">
-        <v>-13.834433184</v>
+        <v>-14.499458688</v>
       </c>
       <c r="Q48">
-        <v>-12.917433184</v>
+        <v>-13.582458688</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.07956019903544134</v>
+        <v>0.08019718392290248</v>
       </c>
       <c r="T48">
-        <v>0.7796812710263586</v>
+        <v>0.7943922384042144</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1205080556350852</v>
+        <v>0.11794405445136</v>
       </c>
       <c r="W48">
-        <v>0.1766019824284749</v>
+        <v>0.1771168338661669</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5477638892503874</v>
+        <v>0.5361093384152729</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1257494193962368</v>
+        <v>0.1272994193962368</v>
       </c>
       <c r="C49">
-        <v>-17.20162523227788</v>
+        <v>-23.80052654578282</v>
       </c>
       <c r="D49">
-        <v>164.3603747677221</v>
+        <v>162.0074734542172</v>
       </c>
       <c r="E49">
-        <v>70.36199999999999</v>
+        <v>74.608</v>
       </c>
       <c r="F49">
-        <v>199.562</v>
+        <v>203.808</v>
       </c>
       <c r="G49">
         <v>18</v>
@@ -5305,37 +5305,37 @@
         <v>21.483</v>
       </c>
       <c r="M49">
-        <v>40.0720496</v>
+        <v>40.9246464</v>
       </c>
       <c r="N49">
-        <v>-18.5890496</v>
+        <v>-19.4416464</v>
       </c>
       <c r="O49">
-        <v>-4.089590912</v>
+        <v>-4.277162208000001</v>
       </c>
       <c r="P49">
-        <v>-14.499458688</v>
+        <v>-15.164484192</v>
       </c>
       <c r="Q49">
-        <v>-13.582458688</v>
+        <v>-14.247484192</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08019718392290248</v>
+        <v>0.08085866822911215</v>
       </c>
       <c r="T49">
-        <v>0.7943922384042144</v>
+        <v>0.80966901221968</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.11794405445136</v>
+        <v>0.11548688665029</v>
       </c>
       <c r="W49">
-        <v>0.1771168338661669</v>
+        <v>0.1776102331606218</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5361093384152729</v>
+        <v>0.5249403938649546</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1272994193962368</v>
+        <v>0.1288494193962368</v>
       </c>
       <c r="C50">
-        <v>-23.80052654578279</v>
+        <v>-30.33301269762541</v>
       </c>
       <c r="D50">
-        <v>162.0074734542172</v>
+        <v>159.7209873023746</v>
       </c>
       <c r="E50">
-        <v>74.60799999999998</v>
+        <v>78.85399999999998</v>
       </c>
       <c r="F50">
-        <v>203.808</v>
+        <v>208.054</v>
       </c>
       <c r="G50">
         <v>18</v>
@@ -5387,37 +5387,37 @@
         <v>21.483</v>
       </c>
       <c r="M50">
-        <v>40.92464639999999</v>
+        <v>41.77724319999999</v>
       </c>
       <c r="N50">
-        <v>-19.4416464</v>
+        <v>-20.2942432</v>
       </c>
       <c r="O50">
-        <v>-4.277162207999999</v>
+        <v>-4.464733503999999</v>
       </c>
       <c r="P50">
-        <v>-15.164484192</v>
+        <v>-15.829509696</v>
       </c>
       <c r="Q50">
-        <v>-14.247484192</v>
+        <v>-14.912509696</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08085866822911215</v>
+        <v>0.08154609309634965</v>
       </c>
       <c r="T50">
-        <v>0.80966901221968</v>
+        <v>0.8255448752043797</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.11548688665029</v>
+        <v>0.113130011412529</v>
       </c>
       <c r="W50">
-        <v>0.1776102331606218</v>
+        <v>0.1780834937083642</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5249403938649547</v>
+        <v>0.5142273246024046</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1288494193962368</v>
+        <v>0.1303994193962368</v>
       </c>
       <c r="C51">
-        <v>-30.33301269762541</v>
+        <v>-36.8018565958501</v>
       </c>
       <c r="D51">
-        <v>159.7209873023746</v>
+        <v>157.4981434041499</v>
       </c>
       <c r="E51">
-        <v>78.85399999999998</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F51">
-        <v>208.054</v>
+        <v>212.3</v>
       </c>
       <c r="G51">
         <v>18</v>
@@ -5469,37 +5469,37 @@
         <v>21.483</v>
       </c>
       <c r="M51">
-        <v>41.77724319999999</v>
+        <v>42.62983999999999</v>
       </c>
       <c r="N51">
-        <v>-20.2942432</v>
+        <v>-21.14684</v>
       </c>
       <c r="O51">
-        <v>-4.464733503999999</v>
+        <v>-4.6523048</v>
       </c>
       <c r="P51">
-        <v>-15.829509696</v>
+        <v>-16.4945352</v>
       </c>
       <c r="Q51">
-        <v>-14.912509696</v>
+        <v>-15.5775352</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08154609309634965</v>
+        <v>0.08226101495827665</v>
       </c>
       <c r="T51">
-        <v>0.8255448752043797</v>
+        <v>0.8420557727084672</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.113130011412529</v>
+        <v>0.1108674111842784</v>
       </c>
       <c r="W51">
-        <v>0.1780834937083642</v>
+        <v>0.1785378238341969</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5142273246024046</v>
+        <v>0.5039427781103565</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1303994193962368</v>
+        <v>0.14995822450459</v>
       </c>
       <c r="C52">
-        <v>-36.8018565958501</v>
+        <v>-64.57496310628852</v>
       </c>
       <c r="D52">
-        <v>157.4981434041499</v>
+        <v>133.9710368937115</v>
       </c>
       <c r="E52">
-        <v>83.09999999999999</v>
+        <v>87.346</v>
       </c>
       <c r="F52">
-        <v>212.3</v>
+        <v>216.546</v>
       </c>
       <c r="G52">
         <v>18</v>
@@ -5551,45 +5551,45 @@
         <v>21.483</v>
       </c>
       <c r="M52">
-        <v>42.62983999999999</v>
+        <v>51.0615468</v>
       </c>
       <c r="N52">
-        <v>-21.14684</v>
+        <v>-29.57854680000001</v>
       </c>
       <c r="O52">
-        <v>-4.6523048</v>
+        <v>-6.507280296000001</v>
       </c>
       <c r="P52">
-        <v>-16.4945352</v>
+        <v>-23.071266504</v>
       </c>
       <c r="Q52">
-        <v>-15.5775352</v>
+        <v>-22.154266504</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08226101495827665</v>
+        <v>0.08332920936222758</v>
       </c>
       <c r="T52">
-        <v>0.8420557727084672</v>
+        <v>0.8667253894278885</v>
       </c>
       <c r="U52">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.1108674111842784</v>
+        <v>0.09256006322158652</v>
       </c>
       <c r="W52">
-        <v>0.1785378238341969</v>
+        <v>0.2139743370923499</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.5039427781103565</v>
+        <v>0.4207275600981206</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.14995822450459</v>
+        <v>0.15185822450459</v>
       </c>
       <c r="C53">
-        <v>-64.57496310628852</v>
+        <v>-70.7372406913419</v>
       </c>
       <c r="D53">
-        <v>133.9710368937115</v>
+        <v>132.0547593086581</v>
       </c>
       <c r="E53">
-        <v>87.346</v>
+        <v>91.59200000000001</v>
       </c>
       <c r="F53">
-        <v>216.546</v>
+        <v>220.792</v>
       </c>
       <c r="G53">
         <v>18</v>
@@ -5633,37 +5633,37 @@
         <v>21.483</v>
       </c>
       <c r="M53">
-        <v>51.0615468</v>
+        <v>52.0627536</v>
       </c>
       <c r="N53">
-        <v>-29.57854680000001</v>
+        <v>-30.5797536</v>
       </c>
       <c r="O53">
-        <v>-6.507280296000001</v>
+        <v>-6.727545792000001</v>
       </c>
       <c r="P53">
-        <v>-23.071266504</v>
+        <v>-23.852207808</v>
       </c>
       <c r="Q53">
-        <v>-22.154266504</v>
+        <v>-22.935207808</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08332920936222758</v>
+        <v>0.08411106789060732</v>
       </c>
       <c r="T53">
-        <v>0.8667253894278885</v>
+        <v>0.8847821683743028</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.09256006322158652</v>
+        <v>0.0907800620057868</v>
       </c>
       <c r="W53">
-        <v>0.2139743370923499</v>
+        <v>0.2143940613790355</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4207275600981206</v>
+        <v>0.412636645480849</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.15185822450459</v>
+        <v>0.15375822450459</v>
       </c>
       <c r="C54">
-        <v>-70.7372406913419</v>
+        <v>-76.84547173353639</v>
       </c>
       <c r="D54">
-        <v>132.0547593086581</v>
+        <v>130.1925282664636</v>
       </c>
       <c r="E54">
-        <v>91.59200000000001</v>
+        <v>95.83799999999999</v>
       </c>
       <c r="F54">
-        <v>220.792</v>
+        <v>225.038</v>
       </c>
       <c r="G54">
         <v>18</v>
@@ -5715,37 +5715,37 @@
         <v>21.483</v>
       </c>
       <c r="M54">
-        <v>52.0627536</v>
+        <v>53.0639604</v>
       </c>
       <c r="N54">
-        <v>-30.5797536</v>
+        <v>-31.5809604</v>
       </c>
       <c r="O54">
-        <v>-6.727545792000001</v>
+        <v>-6.947811288</v>
       </c>
       <c r="P54">
-        <v>-23.852207808</v>
+        <v>-24.633149112</v>
       </c>
       <c r="Q54">
-        <v>-22.935207808</v>
+        <v>-23.716149112</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.08411106789060732</v>
+        <v>0.08492619699466281</v>
       </c>
       <c r="T54">
-        <v>0.8847821683743028</v>
+        <v>0.903607320892905</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.0907800620057868</v>
+        <v>0.08906723064718704</v>
       </c>
       <c r="W54">
-        <v>0.2143940613790355</v>
+        <v>0.2147979470133933</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.412636645480849</v>
+        <v>0.4048510483963047</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.15375822450459</v>
+        <v>0.1556582245045899</v>
       </c>
       <c r="C55">
-        <v>-76.84547173353639</v>
+        <v>-82.90191092399604</v>
       </c>
       <c r="D55">
-        <v>130.1925282664636</v>
+        <v>128.382089076004</v>
       </c>
       <c r="E55">
-        <v>95.83799999999999</v>
+        <v>100.084</v>
       </c>
       <c r="F55">
-        <v>225.038</v>
+        <v>229.284</v>
       </c>
       <c r="G55">
         <v>18</v>
@@ -5797,37 +5797,37 @@
         <v>21.483</v>
       </c>
       <c r="M55">
-        <v>53.0639604</v>
+        <v>54.0651672</v>
       </c>
       <c r="N55">
-        <v>-31.5809604</v>
+        <v>-32.5821672</v>
       </c>
       <c r="O55">
-        <v>-6.947811288</v>
+        <v>-7.168076784</v>
       </c>
       <c r="P55">
-        <v>-24.633149112</v>
+        <v>-25.414090416</v>
       </c>
       <c r="Q55">
-        <v>-23.716149112</v>
+        <v>-24.497090416</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.08492619699466281</v>
+        <v>0.08577676649454677</v>
       </c>
       <c r="T55">
-        <v>0.903607320892905</v>
+        <v>0.9232509583036204</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.08906723064718704</v>
+        <v>0.08741783748705395</v>
       </c>
       <c r="W55">
-        <v>0.2147979470133933</v>
+        <v>0.2151868739205527</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4048510483963047</v>
+        <v>0.3973538067593362</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1556582245045899</v>
+        <v>0.15755822450459</v>
       </c>
       <c r="C56">
-        <v>-82.90191092399604</v>
+        <v>-88.90868926022651</v>
       </c>
       <c r="D56">
-        <v>128.382089076004</v>
+        <v>126.6213107397735</v>
       </c>
       <c r="E56">
-        <v>100.084</v>
+        <v>104.33</v>
       </c>
       <c r="F56">
-        <v>229.284</v>
+        <v>233.53</v>
       </c>
       <c r="G56">
         <v>18</v>
@@ -5879,37 +5879,37 @@
         <v>21.483</v>
       </c>
       <c r="M56">
-        <v>54.0651672</v>
+        <v>55.066374</v>
       </c>
       <c r="N56">
-        <v>-32.5821672</v>
+        <v>-33.58337400000001</v>
       </c>
       <c r="O56">
-        <v>-7.168076784</v>
+        <v>-7.388342280000002</v>
       </c>
       <c r="P56">
-        <v>-25.414090416</v>
+        <v>-26.19503172</v>
       </c>
       <c r="Q56">
-        <v>-24.497090416</v>
+        <v>-25.27803172</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.08577676649454677</v>
+        <v>0.08666513908331448</v>
       </c>
       <c r="T56">
-        <v>0.9232509583036204</v>
+        <v>0.9437676462659231</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.08741783748705395</v>
+        <v>0.08582842226001659</v>
       </c>
       <c r="W56">
-        <v>0.2151868739205527</v>
+        <v>0.2155616580310881</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3973538067593362</v>
+        <v>0.3901291920909845</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.15755822450459</v>
+        <v>0.15945822450459</v>
       </c>
       <c r="C57">
-        <v>-88.90868926022651</v>
+        <v>-94.86782241372836</v>
       </c>
       <c r="D57">
-        <v>126.6213107397735</v>
+        <v>124.9081775862716</v>
       </c>
       <c r="E57">
-        <v>104.33</v>
+        <v>108.576</v>
       </c>
       <c r="F57">
-        <v>233.53</v>
+        <v>237.776</v>
       </c>
       <c r="G57">
         <v>18</v>
@@ -5961,37 +5961,37 @@
         <v>21.483</v>
       </c>
       <c r="M57">
-        <v>55.066374</v>
+        <v>56.0675808</v>
       </c>
       <c r="N57">
-        <v>-33.58337400000001</v>
+        <v>-34.5845808</v>
       </c>
       <c r="O57">
-        <v>-7.388342280000002</v>
+        <v>-7.608607776000001</v>
       </c>
       <c r="P57">
-        <v>-26.19503172</v>
+        <v>-26.97597302400001</v>
       </c>
       <c r="Q57">
-        <v>-25.27803172</v>
+        <v>-26.058973024</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.08666513908331448</v>
+        <v>0.08759389224429891</v>
       </c>
       <c r="T57">
-        <v>0.9437676462659231</v>
+        <v>0.965216910953785</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.08582842226001659</v>
+        <v>0.0842957718625163</v>
       </c>
       <c r="W57">
-        <v>0.2155616580310881</v>
+        <v>0.2159230569948186</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3901291920909845</v>
+        <v>0.3831625993750741</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.15945822450459</v>
+        <v>0.16135822450459</v>
       </c>
       <c r="C58">
-        <v>-94.86782241372836</v>
+        <v>-100.7812184274166</v>
       </c>
       <c r="D58">
-        <v>124.9081775862716</v>
+        <v>123.2407815725834</v>
       </c>
       <c r="E58">
-        <v>108.576</v>
+        <v>112.822</v>
       </c>
       <c r="F58">
-        <v>237.776</v>
+        <v>242.022</v>
       </c>
       <c r="G58">
         <v>18</v>
@@ -6043,37 +6043,37 @@
         <v>21.483</v>
       </c>
       <c r="M58">
-        <v>56.0675808</v>
+        <v>57.06878760000001</v>
       </c>
       <c r="N58">
-        <v>-34.5845808</v>
+        <v>-35.58578760000001</v>
       </c>
       <c r="O58">
-        <v>-7.608607776000001</v>
+        <v>-7.828873272000003</v>
       </c>
       <c r="P58">
-        <v>-26.97597302400001</v>
+        <v>-27.75691432800001</v>
       </c>
       <c r="Q58">
-        <v>-26.058973024</v>
+        <v>-26.83991432800001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.08759389224429891</v>
+        <v>0.08856584322672445</v>
       </c>
       <c r="T58">
-        <v>0.965216910953785</v>
+        <v>0.987663815859687</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.0842957718625163</v>
+        <v>0.08281689867194583</v>
       </c>
       <c r="W58">
-        <v>0.2159230569948186</v>
+        <v>0.2162717752931552</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3831625993750741</v>
+        <v>0.3764404485088447</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.16135822450459</v>
+        <v>0.16325822450459</v>
       </c>
       <c r="C59">
-        <v>-100.7812184274166</v>
+        <v>-106.6506848046451</v>
       </c>
       <c r="D59">
-        <v>123.2407815725834</v>
+        <v>121.6173151953549</v>
       </c>
       <c r="E59">
-        <v>112.822</v>
+        <v>117.068</v>
       </c>
       <c r="F59">
-        <v>242.022</v>
+        <v>246.268</v>
       </c>
       <c r="G59">
         <v>18</v>
@@ -6125,37 +6125,37 @@
         <v>21.483</v>
       </c>
       <c r="M59">
-        <v>57.06878760000001</v>
+        <v>58.06999440000001</v>
       </c>
       <c r="N59">
-        <v>-35.58578760000001</v>
+        <v>-36.58699440000001</v>
       </c>
       <c r="O59">
-        <v>-7.828873272000003</v>
+        <v>-8.049138768000002</v>
       </c>
       <c r="P59">
-        <v>-27.75691432800001</v>
+        <v>-28.53785563200001</v>
       </c>
       <c r="Q59">
-        <v>-26.83991432800001</v>
+        <v>-27.620855632</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.08856584322672445</v>
+        <v>0.08958407758926551</v>
       </c>
       <c r="T59">
-        <v>0.987663815859687</v>
+        <v>1.011179620999203</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.08281689867194583</v>
+        <v>0.08138902110863643</v>
       </c>
       <c r="W59">
-        <v>0.2162717752931552</v>
+        <v>0.2166084688225835</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3764404485088447</v>
+        <v>0.3699500959483474</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.16325822450459</v>
+        <v>0.1651582245045899</v>
       </c>
       <c r="C60">
-        <v>-106.650684804645</v>
+        <v>-112.4779350452088</v>
       </c>
       <c r="D60">
-        <v>121.6173151953549</v>
+        <v>120.0360649547912</v>
       </c>
       <c r="E60">
-        <v>117.068</v>
+        <v>121.314</v>
       </c>
       <c r="F60">
-        <v>246.268</v>
+        <v>250.514</v>
       </c>
       <c r="G60">
         <v>18</v>
@@ -6207,37 +6207,37 @@
         <v>21.483</v>
       </c>
       <c r="M60">
-        <v>58.0699944</v>
+        <v>59.07120119999999</v>
       </c>
       <c r="N60">
-        <v>-36.5869944</v>
+        <v>-37.58820119999999</v>
       </c>
       <c r="O60">
-        <v>-8.049138768000001</v>
+        <v>-8.269404263999999</v>
       </c>
       <c r="P60">
-        <v>-28.537855632</v>
+        <v>-29.31879693599999</v>
       </c>
       <c r="Q60">
-        <v>-27.620855632</v>
+        <v>-28.40179693599999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.08958407758926551</v>
+        <v>0.090651981920711</v>
       </c>
       <c r="T60">
-        <v>1.011179620999203</v>
+        <v>1.03584253858455</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.08138902110863644</v>
+        <v>0.08000954617459176</v>
       </c>
       <c r="W60">
-        <v>0.2166084688225835</v>
+        <v>0.2169337490120313</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3699500959483474</v>
+        <v>0.3636797553390535</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1651582245045899</v>
+        <v>0.16705822450459</v>
       </c>
       <c r="C61">
-        <v>-112.4779350452088</v>
+        <v>-118.2645946780097</v>
       </c>
       <c r="D61">
-        <v>120.0360649547912</v>
+        <v>118.4954053219903</v>
       </c>
       <c r="E61">
-        <v>121.314</v>
+        <v>125.56</v>
       </c>
       <c r="F61">
-        <v>250.514</v>
+        <v>254.76</v>
       </c>
       <c r="G61">
         <v>18</v>
@@ -6289,37 +6289,37 @@
         <v>21.483</v>
       </c>
       <c r="M61">
-        <v>59.07120119999999</v>
+        <v>60.072408</v>
       </c>
       <c r="N61">
-        <v>-37.58820119999999</v>
+        <v>-38.589408</v>
       </c>
       <c r="O61">
-        <v>-8.269404263999999</v>
+        <v>-8.48966976</v>
       </c>
       <c r="P61">
-        <v>-29.31879693599999</v>
+        <v>-30.09973824</v>
       </c>
       <c r="Q61">
-        <v>-28.40179693599999</v>
+        <v>-29.18273824</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.090651981920711</v>
+        <v>0.09177328146872879</v>
       </c>
       <c r="T61">
-        <v>1.03584253858455</v>
+        <v>1.061738602049163</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.08000954617459176</v>
+        <v>0.07867605373834856</v>
       </c>
       <c r="W61">
-        <v>0.2169337490120313</v>
+        <v>0.2172481865284974</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3636797553390535</v>
+        <v>0.3576184260834026</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.16705822450459</v>
+        <v>0.16895822450459</v>
       </c>
       <c r="C62">
-        <v>-118.2645946780097</v>
+        <v>-124.0122068350344</v>
       </c>
       <c r="D62">
-        <v>118.4954053219903</v>
+        <v>116.9937931649656</v>
       </c>
       <c r="E62">
-        <v>125.56</v>
+        <v>129.806</v>
       </c>
       <c r="F62">
-        <v>254.76</v>
+        <v>259.006</v>
       </c>
       <c r="G62">
         <v>18</v>
@@ -6371,37 +6371,37 @@
         <v>21.483</v>
       </c>
       <c r="M62">
-        <v>60.072408</v>
+        <v>61.07361479999999</v>
       </c>
       <c r="N62">
-        <v>-38.589408</v>
+        <v>-39.5906148</v>
       </c>
       <c r="O62">
-        <v>-8.48966976</v>
+        <v>-8.709935256</v>
       </c>
       <c r="P62">
-        <v>-30.09973824</v>
+        <v>-30.880679544</v>
       </c>
       <c r="Q62">
-        <v>-29.18273824</v>
+        <v>-29.96367954399999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09177328146872879</v>
+        <v>0.09295208355767055</v>
       </c>
       <c r="T62">
-        <v>1.061738602049163</v>
+        <v>1.088962668768373</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.07867605373834856</v>
+        <v>0.07738628236558875</v>
       </c>
       <c r="W62">
-        <v>0.2172481865284974</v>
+        <v>0.2175523146181942</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3576184260834026</v>
+        <v>0.3517558289344943</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.16895822450459</v>
+        <v>0.17085822450459</v>
       </c>
       <c r="C63">
-        <v>-124.0122068350344</v>
+        <v>-129.7222374068247</v>
       </c>
       <c r="D63">
-        <v>116.9937931649656</v>
+        <v>115.5297625931752</v>
       </c>
       <c r="E63">
-        <v>129.806</v>
+        <v>134.052</v>
       </c>
       <c r="F63">
-        <v>259.006</v>
+        <v>263.252</v>
       </c>
       <c r="G63">
         <v>18</v>
@@ -6453,37 +6453,37 @@
         <v>21.483</v>
       </c>
       <c r="M63">
-        <v>61.07361479999999</v>
+        <v>62.07482159999999</v>
       </c>
       <c r="N63">
-        <v>-39.5906148</v>
+        <v>-40.5918216</v>
       </c>
       <c r="O63">
-        <v>-8.709935256</v>
+        <v>-8.930200751999999</v>
       </c>
       <c r="P63">
-        <v>-30.880679544</v>
+        <v>-31.661620848</v>
       </c>
       <c r="Q63">
-        <v>-29.96367954399999</v>
+        <v>-30.744620848</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.09295208355767055</v>
+        <v>0.09419292786181978</v>
       </c>
       <c r="T63">
-        <v>1.088962668768373</v>
+        <v>1.117619581104383</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.07738628236558875</v>
+        <v>0.07613811652098249</v>
       </c>
       <c r="W63">
-        <v>0.2175523146181942</v>
+        <v>0.2178466321243523</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3517558289344943</v>
+        <v>0.3460823478226476</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.17085822450459</v>
+        <v>0.17275822450459</v>
       </c>
       <c r="C64">
-        <v>-129.7222374068247</v>
+        <v>-135.3960798156467</v>
       </c>
       <c r="D64">
-        <v>115.5297625931752</v>
+        <v>114.1019201843533</v>
       </c>
       <c r="E64">
-        <v>134.052</v>
+        <v>138.298</v>
       </c>
       <c r="F64">
-        <v>263.252</v>
+        <v>267.498</v>
       </c>
       <c r="G64">
         <v>18</v>
@@ -6535,37 +6535,37 @@
         <v>21.483</v>
       </c>
       <c r="M64">
-        <v>62.07482159999999</v>
+        <v>63.0760284</v>
       </c>
       <c r="N64">
-        <v>-40.5918216</v>
+        <v>-41.5930284</v>
       </c>
       <c r="O64">
-        <v>-8.930200751999999</v>
+        <v>-9.150466248000001</v>
       </c>
       <c r="P64">
-        <v>-31.661620848</v>
+        <v>-32.442562152</v>
       </c>
       <c r="Q64">
-        <v>-30.744620848</v>
+        <v>-31.525562152</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.09419292786181978</v>
+        <v>0.09550084483105814</v>
       </c>
       <c r="T64">
-        <v>1.117619581104383</v>
+        <v>1.147825515728825</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.07613811652098249</v>
+        <v>0.07492957498890337</v>
       </c>
       <c r="W64">
-        <v>0.2178466321243523</v>
+        <v>0.2181316062176166</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3460823478226476</v>
+        <v>0.3405889772222881</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.17275822450459</v>
+        <v>0.17465822450459</v>
       </c>
       <c r="C65">
-        <v>-135.3960798156467</v>
+        <v>-141.0350594390277</v>
       </c>
       <c r="D65">
-        <v>114.1019201843533</v>
+        <v>112.7089405609723</v>
       </c>
       <c r="E65">
-        <v>138.298</v>
+        <v>142.544</v>
       </c>
       <c r="F65">
-        <v>267.498</v>
+        <v>271.744</v>
       </c>
       <c r="G65">
         <v>18</v>
@@ -6617,37 +6617,37 @@
         <v>21.483</v>
       </c>
       <c r="M65">
-        <v>63.0760284</v>
+        <v>64.07723519999999</v>
       </c>
       <c r="N65">
-        <v>-41.5930284</v>
+        <v>-42.59423519999999</v>
       </c>
       <c r="O65">
-        <v>-9.150466248000001</v>
+        <v>-9.370731743999999</v>
       </c>
       <c r="P65">
-        <v>-32.442562152</v>
+        <v>-33.223503456</v>
       </c>
       <c r="Q65">
-        <v>-31.525562152</v>
+        <v>-32.30650345599999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.09550084483105814</v>
+        <v>0.09688142385414311</v>
       </c>
       <c r="T65">
-        <v>1.147825515728825</v>
+        <v>1.179709557832404</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.07492957498890337</v>
+        <v>0.07375880037970177</v>
       </c>
       <c r="W65">
-        <v>0.2181316062176166</v>
+        <v>0.2184076748704663</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3405889772222881</v>
+        <v>0.3352672744531899</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.17465822450459</v>
+        <v>0.17655822450459</v>
       </c>
       <c r="C66">
-        <v>-141.0350594390277</v>
+        <v>-146.6404377131824</v>
       </c>
       <c r="D66">
-        <v>112.7089405609723</v>
+        <v>111.3495622868176</v>
       </c>
       <c r="E66">
-        <v>142.544</v>
+        <v>146.79</v>
       </c>
       <c r="F66">
-        <v>271.744</v>
+        <v>275.99</v>
       </c>
       <c r="G66">
         <v>18</v>
@@ -6699,37 +6699,37 @@
         <v>21.483</v>
       </c>
       <c r="M66">
-        <v>64.07723519999999</v>
+        <v>65.07844200000001</v>
       </c>
       <c r="N66">
-        <v>-42.59423519999999</v>
+        <v>-43.59544200000001</v>
       </c>
       <c r="O66">
-        <v>-9.370731743999999</v>
+        <v>-9.590997240000004</v>
       </c>
       <c r="P66">
-        <v>-33.223503456</v>
+        <v>-34.00444476000001</v>
       </c>
       <c r="Q66">
-        <v>-32.30650345599999</v>
+        <v>-33.08744476000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.09688142385414311</v>
+        <v>0.09834089310711863</v>
       </c>
       <c r="T66">
-        <v>1.179709557832404</v>
+        <v>1.213415545199044</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.07375880037970177</v>
+        <v>0.07262404960462941</v>
       </c>
       <c r="W66">
-        <v>0.2184076748704663</v>
+        <v>0.2186752491032284</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3352672744531899</v>
+        <v>0.3301093163846792</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.17655822450459</v>
+        <v>0.17845822450459</v>
       </c>
       <c r="C67">
-        <v>-146.6404377131824</v>
+        <v>-152.2134159430282</v>
       </c>
       <c r="D67">
-        <v>111.3495622868176</v>
+        <v>110.0225840569718</v>
       </c>
       <c r="E67">
-        <v>146.79</v>
+        <v>151.036</v>
       </c>
       <c r="F67">
-        <v>275.99</v>
+        <v>280.236</v>
       </c>
       <c r="G67">
         <v>18</v>
@@ -6781,37 +6781,37 @@
         <v>21.483</v>
       </c>
       <c r="M67">
-        <v>65.07844200000001</v>
+        <v>66.0796488</v>
       </c>
       <c r="N67">
-        <v>-43.59544200000001</v>
+        <v>-44.5966488</v>
       </c>
       <c r="O67">
-        <v>-9.590997240000004</v>
+        <v>-9.811262736000002</v>
       </c>
       <c r="P67">
-        <v>-34.00444476000001</v>
+        <v>-34.785386064</v>
       </c>
       <c r="Q67">
-        <v>-33.08744476000001</v>
+        <v>-33.868386064</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.09834089310711863</v>
+        <v>0.09988621349262211</v>
       </c>
       <c r="T67">
-        <v>1.213415545199044</v>
+        <v>1.249104237704898</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.07262404960462941</v>
+        <v>0.0715236852166805</v>
       </c>
       <c r="W67">
-        <v>0.2186752491032284</v>
+        <v>0.2189347150259068</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3301093163846792</v>
+        <v>0.3251076600758205</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.17845822450459</v>
+        <v>0.18035822450459</v>
       </c>
       <c r="C68">
-        <v>-152.2134159430282</v>
+        <v>-157.7551388429818</v>
       </c>
       <c r="D68">
-        <v>110.0225840569718</v>
+        <v>108.7268611570182</v>
       </c>
       <c r="E68">
-        <v>151.036</v>
+        <v>155.282</v>
       </c>
       <c r="F68">
-        <v>280.236</v>
+        <v>284.482</v>
       </c>
       <c r="G68">
         <v>18</v>
@@ -6863,37 +6863,37 @@
         <v>21.483</v>
       </c>
       <c r="M68">
-        <v>66.0796488</v>
+        <v>67.08085559999999</v>
       </c>
       <c r="N68">
-        <v>-44.5966488</v>
+        <v>-45.5978556</v>
       </c>
       <c r="O68">
-        <v>-9.811262736000002</v>
+        <v>-10.031528232</v>
       </c>
       <c r="P68">
-        <v>-34.785386064</v>
+        <v>-35.566327368</v>
       </c>
       <c r="Q68">
-        <v>-33.868386064</v>
+        <v>-34.64932736799999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.09988621349262211</v>
+        <v>0.1015251896590652</v>
       </c>
       <c r="T68">
-        <v>1.249104237704898</v>
+        <v>1.286955881271713</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0715236852166805</v>
+        <v>0.0704561675268793</v>
       </c>
       <c r="W68">
-        <v>0.2189347150259068</v>
+        <v>0.2191864356971619</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3251076600758205</v>
+        <v>0.3202553069403605</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.18035822450459</v>
+        <v>0.18225822450459</v>
       </c>
       <c r="C69">
-        <v>-157.7551388429818</v>
+        <v>-163.2666978304692</v>
       </c>
       <c r="D69">
-        <v>108.7268611570182</v>
+        <v>107.4613021695308</v>
       </c>
       <c r="E69">
-        <v>155.282</v>
+        <v>159.528</v>
       </c>
       <c r="F69">
-        <v>284.482</v>
+        <v>288.728</v>
       </c>
       <c r="G69">
         <v>18</v>
@@ -6945,37 +6945,37 @@
         <v>21.483</v>
       </c>
       <c r="M69">
-        <v>67.08085559999999</v>
+        <v>68.0820624</v>
       </c>
       <c r="N69">
-        <v>-45.5978556</v>
+        <v>-46.5990624</v>
       </c>
       <c r="O69">
-        <v>-10.031528232</v>
+        <v>-10.251793728</v>
       </c>
       <c r="P69">
-        <v>-35.566327368</v>
+        <v>-36.347268672</v>
       </c>
       <c r="Q69">
-        <v>-34.64932736799999</v>
+        <v>-35.430268672</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1015251896590652</v>
+        <v>0.103266601835911</v>
       </c>
       <c r="T69">
-        <v>1.286955881271713</v>
+        <v>1.327173252561454</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0704561675268793</v>
+        <v>0.0694200474161899</v>
       </c>
       <c r="W69">
-        <v>0.2191864356971619</v>
+        <v>0.2194307528192624</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3202553069403605</v>
+        <v>0.3155456700735905</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.18225822450459</v>
+        <v>0.18415822450459</v>
       </c>
       <c r="C70">
-        <v>-163.2666978304692</v>
+        <v>-168.7491340920687</v>
       </c>
       <c r="D70">
-        <v>107.4613021695308</v>
+        <v>106.2248659079313</v>
       </c>
       <c r="E70">
-        <v>159.528</v>
+        <v>163.774</v>
       </c>
       <c r="F70">
-        <v>288.728</v>
+        <v>292.974</v>
       </c>
       <c r="G70">
         <v>18</v>
@@ -7027,37 +7027,37 @@
         <v>21.483</v>
       </c>
       <c r="M70">
-        <v>68.0820624</v>
+        <v>69.0832692</v>
       </c>
       <c r="N70">
-        <v>-46.5990624</v>
+        <v>-47.60026920000001</v>
       </c>
       <c r="O70">
-        <v>-10.251793728</v>
+        <v>-10.472059224</v>
       </c>
       <c r="P70">
-        <v>-36.347268672</v>
+        <v>-37.12820997600001</v>
       </c>
       <c r="Q70">
-        <v>-35.430268672</v>
+        <v>-36.21120997600001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.103266601835911</v>
+        <v>0.1051203631854565</v>
       </c>
       <c r="T70">
-        <v>1.327173252561454</v>
+        <v>1.369985292966663</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0694200474161899</v>
+        <v>0.068413959772477</v>
       </c>
       <c r="W70">
-        <v>0.2194307528192624</v>
+        <v>0.2196679882856499</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3155456700735905</v>
+        <v>0.3109725444203499</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.18415822450459</v>
+        <v>0.18605822450459</v>
       </c>
       <c r="C71">
-        <v>-168.7491340920687</v>
+        <v>-174.2034414403888</v>
       </c>
       <c r="D71">
-        <v>106.2248659079313</v>
+        <v>105.0165585596112</v>
       </c>
       <c r="E71">
-        <v>163.774</v>
+        <v>168.02</v>
       </c>
       <c r="F71">
-        <v>292.974</v>
+        <v>297.22</v>
       </c>
       <c r="G71">
         <v>18</v>
@@ -7109,37 +7109,37 @@
         <v>21.483</v>
       </c>
       <c r="M71">
-        <v>69.0832692</v>
+        <v>70.08447600000001</v>
       </c>
       <c r="N71">
-        <v>-47.60026920000001</v>
+        <v>-48.60147600000001</v>
       </c>
       <c r="O71">
-        <v>-10.472059224</v>
+        <v>-10.69232472</v>
       </c>
       <c r="P71">
-        <v>-37.12820997600001</v>
+        <v>-37.90915128000001</v>
       </c>
       <c r="Q71">
-        <v>-36.21120997600001</v>
+        <v>-36.99215128000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1051203631854565</v>
+        <v>0.1070977086249717</v>
       </c>
       <c r="T71">
-        <v>1.369985292966663</v>
+        <v>1.415651469398885</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.068413959772477</v>
+        <v>0.06743661749001303</v>
       </c>
       <c r="W71">
-        <v>0.2196679882856499</v>
+        <v>0.2198984455958549</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3109725444203499</v>
+        <v>0.3065300795000593</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.18605822450459</v>
+        <v>0.18795822450459</v>
       </c>
       <c r="C72">
-        <v>-174.2034414403888</v>
+        <v>-179.6305689781578</v>
       </c>
       <c r="D72">
-        <v>105.0165585596112</v>
+        <v>103.8354310218422</v>
       </c>
       <c r="E72">
-        <v>168.02</v>
+        <v>172.266</v>
       </c>
       <c r="F72">
-        <v>297.22</v>
+        <v>301.466</v>
       </c>
       <c r="G72">
         <v>18</v>
@@ -7191,37 +7191,37 @@
         <v>21.483</v>
       </c>
       <c r="M72">
-        <v>70.08447600000001</v>
+        <v>71.0856828</v>
       </c>
       <c r="N72">
-        <v>-48.60147600000001</v>
+        <v>-49.6026828</v>
       </c>
       <c r="O72">
-        <v>-10.69232472</v>
+        <v>-10.912590216</v>
       </c>
       <c r="P72">
-        <v>-37.90915128000001</v>
+        <v>-38.690092584</v>
       </c>
       <c r="Q72">
-        <v>-36.99215128000001</v>
+        <v>-37.773092584</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1070977086249717</v>
+        <v>0.109211422715488</v>
       </c>
       <c r="T72">
-        <v>1.415651469398885</v>
+        <v>1.464467037309191</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.06743661749001303</v>
+        <v>0.06648680597606919</v>
       </c>
       <c r="W72">
-        <v>0.2198984455958549</v>
+        <v>0.2201224111508429</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3065300795000593</v>
+        <v>0.3022127544366782</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.18795822450459</v>
+        <v>0.18985822450459</v>
       </c>
       <c r="C73">
-        <v>-179.6305689781577</v>
+        <v>-185.0314235845335</v>
       </c>
       <c r="D73">
-        <v>103.8354310218422</v>
+        <v>102.6805764154665</v>
       </c>
       <c r="E73">
-        <v>172.266</v>
+        <v>176.512</v>
       </c>
       <c r="F73">
-        <v>301.466</v>
+        <v>305.712</v>
       </c>
       <c r="G73">
         <v>18</v>
@@ -7273,37 +7273,37 @@
         <v>21.483</v>
       </c>
       <c r="M73">
-        <v>71.08568279999999</v>
+        <v>72.08688960000001</v>
       </c>
       <c r="N73">
-        <v>-49.60268279999999</v>
+        <v>-50.60388960000001</v>
       </c>
       <c r="O73">
-        <v>-10.912590216</v>
+        <v>-11.132855712</v>
       </c>
       <c r="P73">
-        <v>-38.69009258399999</v>
+        <v>-39.47103388800001</v>
       </c>
       <c r="Q73">
-        <v>-37.77309258399999</v>
+        <v>-38.55403388800001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.109211422715488</v>
+        <v>0.1114761163838983</v>
       </c>
       <c r="T73">
-        <v>1.464467037309191</v>
+        <v>1.516769431498805</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.06648680597606921</v>
+        <v>0.06556337811529045</v>
       </c>
       <c r="W73">
-        <v>0.2201224111508429</v>
+        <v>0.2203401554404145</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3022127544366783</v>
+        <v>0.2980153550695021</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.18985822450459</v>
+        <v>0.19175822450459</v>
       </c>
       <c r="C74">
-        <v>-185.0314235845335</v>
+        <v>-190.4068722373225</v>
       </c>
       <c r="D74">
-        <v>102.6805764154665</v>
+        <v>101.5511277626775</v>
       </c>
       <c r="E74">
-        <v>176.512</v>
+        <v>180.758</v>
       </c>
       <c r="F74">
-        <v>305.712</v>
+        <v>309.958</v>
       </c>
       <c r="G74">
         <v>18</v>
@@ -7355,37 +7355,37 @@
         <v>21.483</v>
       </c>
       <c r="M74">
-        <v>72.08688960000001</v>
+        <v>73.0880964</v>
       </c>
       <c r="N74">
-        <v>-50.60388960000001</v>
+        <v>-51.6050964</v>
       </c>
       <c r="O74">
-        <v>-11.132855712</v>
+        <v>-11.353121208</v>
       </c>
       <c r="P74">
-        <v>-39.47103388800001</v>
+        <v>-40.251975192</v>
       </c>
       <c r="Q74">
-        <v>-38.55403388800001</v>
+        <v>-39.334975192</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1114761163838983</v>
+        <v>0.1139085651388574</v>
       </c>
       <c r="T74">
-        <v>1.516769431498805</v>
+        <v>1.572946077109871</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06556337811529045</v>
+        <v>0.06466524964795771</v>
       </c>
       <c r="W74">
-        <v>0.2203401554404145</v>
+        <v>0.2205519341330116</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2980153550695021</v>
+        <v>0.2939329529452623</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.19175822450459</v>
+        <v>0.19365822450459</v>
       </c>
       <c r="C75">
-        <v>-190.4068722373225</v>
+        <v>-195.7577441836046</v>
       </c>
       <c r="D75">
-        <v>101.5511277626775</v>
+        <v>100.4462558163954</v>
       </c>
       <c r="E75">
-        <v>180.758</v>
+        <v>185.004</v>
       </c>
       <c r="F75">
-        <v>309.958</v>
+        <v>314.204</v>
       </c>
       <c r="G75">
         <v>18</v>
@@ -7437,37 +7437,37 @@
         <v>21.483</v>
       </c>
       <c r="M75">
-        <v>73.0880964</v>
+        <v>74.08930319999999</v>
       </c>
       <c r="N75">
-        <v>-51.6050964</v>
+        <v>-52.60630319999999</v>
       </c>
       <c r="O75">
-        <v>-11.353121208</v>
+        <v>-11.573386704</v>
       </c>
       <c r="P75">
-        <v>-40.251975192</v>
+        <v>-41.03291649599999</v>
       </c>
       <c r="Q75">
-        <v>-39.334975192</v>
+        <v>-40.11591649599999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1139085651388574</v>
+        <v>0.1165281253365058</v>
       </c>
       <c r="T75">
-        <v>1.572946077109871</v>
+        <v>1.633444003152559</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06466524964795771</v>
+        <v>0.06379139492298531</v>
       </c>
       <c r="W75">
-        <v>0.2205519341330116</v>
+        <v>0.2207579890771601</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2939329529452623</v>
+        <v>0.2899608860135696</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.19365822450459</v>
+        <v>0.19555822450459</v>
       </c>
       <c r="C76">
-        <v>-195.7577441836046</v>
+        <v>-201.0848329701856</v>
       </c>
       <c r="D76">
-        <v>100.4462558163954</v>
+        <v>99.36516702981442</v>
       </c>
       <c r="E76">
-        <v>185.004</v>
+        <v>189.25</v>
       </c>
       <c r="F76">
-        <v>314.204</v>
+        <v>318.45</v>
       </c>
       <c r="G76">
         <v>18</v>
@@ -7519,37 +7519,37 @@
         <v>21.483</v>
       </c>
       <c r="M76">
-        <v>74.08930319999999</v>
+        <v>75.09050999999999</v>
       </c>
       <c r="N76">
-        <v>-52.60630319999999</v>
+        <v>-53.60751</v>
       </c>
       <c r="O76">
-        <v>-11.573386704</v>
+        <v>-11.7936522</v>
       </c>
       <c r="P76">
-        <v>-41.03291649599999</v>
+        <v>-41.81385779999999</v>
       </c>
       <c r="Q76">
-        <v>-40.11591649599999</v>
+        <v>-40.89685779999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1165281253365058</v>
+        <v>0.1193572503499661</v>
       </c>
       <c r="T76">
-        <v>1.633444003152559</v>
+        <v>1.698781763278661</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06379139492298531</v>
+        <v>0.06294084299067886</v>
       </c>
       <c r="W76">
-        <v>0.2207579890771601</v>
+        <v>0.220958549222798</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2899608860135696</v>
+        <v>0.286094740866722</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.19555822450459</v>
+        <v>0.19745822450459</v>
       </c>
       <c r="C77">
-        <v>-201.0848329701856</v>
+        <v>-206.3888983443244</v>
       </c>
       <c r="D77">
-        <v>99.36516702981442</v>
+        <v>98.30710165567554</v>
       </c>
       <c r="E77">
-        <v>189.25</v>
+        <v>193.496</v>
       </c>
       <c r="F77">
-        <v>318.45</v>
+        <v>322.696</v>
       </c>
       <c r="G77">
         <v>18</v>
@@ -7601,37 +7601,37 @@
         <v>21.483</v>
       </c>
       <c r="M77">
-        <v>75.09050999999999</v>
+        <v>76.0917168</v>
       </c>
       <c r="N77">
-        <v>-53.60751</v>
+        <v>-54.6087168</v>
       </c>
       <c r="O77">
-        <v>-11.7936522</v>
+        <v>-12.013917696</v>
       </c>
       <c r="P77">
-        <v>-41.81385779999999</v>
+        <v>-42.594799104</v>
       </c>
       <c r="Q77">
-        <v>-40.89685779999999</v>
+        <v>-41.677799104</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1193572503499661</v>
+        <v>0.1224221357812147</v>
       </c>
       <c r="T77">
-        <v>1.698781763278661</v>
+        <v>1.769564336748606</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06294084299067886</v>
+        <v>0.06211267400395939</v>
       </c>
       <c r="W77">
-        <v>0.220958549222798</v>
+        <v>0.2211538314698664</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.286094740866722</v>
+        <v>0.2823303363816335</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.19745822450459</v>
+        <v>0.19935822450459</v>
       </c>
       <c r="C78">
-        <v>-206.3888983443244</v>
+        <v>-211.6706680343043</v>
       </c>
       <c r="D78">
-        <v>98.30710165567554</v>
+        <v>97.27133196569569</v>
       </c>
       <c r="E78">
-        <v>193.496</v>
+        <v>197.742</v>
       </c>
       <c r="F78">
-        <v>322.696</v>
+        <v>326.942</v>
       </c>
       <c r="G78">
         <v>18</v>
@@ -7683,37 +7683,37 @@
         <v>21.483</v>
       </c>
       <c r="M78">
-        <v>76.0917168</v>
+        <v>77.09292360000001</v>
       </c>
       <c r="N78">
-        <v>-54.6087168</v>
+        <v>-55.60992360000001</v>
       </c>
       <c r="O78">
-        <v>-12.013917696</v>
+        <v>-12.234183192</v>
       </c>
       <c r="P78">
-        <v>-42.594799104</v>
+        <v>-43.37574040800001</v>
       </c>
       <c r="Q78">
-        <v>-41.677799104</v>
+        <v>-42.458740408</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1224221357812147</v>
+        <v>0.1257535329890936</v>
       </c>
       <c r="T78">
-        <v>1.769564336748606</v>
+        <v>1.846501916607241</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06211267400395939</v>
+        <v>0.06130601590001185</v>
       </c>
       <c r="W78">
-        <v>0.2211538314698664</v>
+        <v>0.2213440414507772</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2823303363816335</v>
+        <v>0.2786637086364175</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.19935822450459</v>
+        <v>0.20125822450459</v>
       </c>
       <c r="C79">
-        <v>-211.6706680343043</v>
+        <v>-216.9308394186152</v>
       </c>
       <c r="D79">
-        <v>97.27133196569569</v>
+        <v>96.25716058138482</v>
       </c>
       <c r="E79">
-        <v>197.742</v>
+        <v>201.988</v>
       </c>
       <c r="F79">
-        <v>326.942</v>
+        <v>331.188</v>
       </c>
       <c r="G79">
         <v>18</v>
@@ -7765,37 +7765,37 @@
         <v>21.483</v>
       </c>
       <c r="M79">
-        <v>77.09292360000001</v>
+        <v>78.0941304</v>
       </c>
       <c r="N79">
-        <v>-55.60992360000001</v>
+        <v>-56.6111304</v>
       </c>
       <c r="O79">
-        <v>-12.234183192</v>
+        <v>-12.454448688</v>
       </c>
       <c r="P79">
-        <v>-43.37574040800001</v>
+        <v>-44.156681712</v>
       </c>
       <c r="Q79">
-        <v>-42.458740408</v>
+        <v>-43.239681712</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1257535329890936</v>
+        <v>0.1293877844885978</v>
       </c>
       <c r="T79">
-        <v>1.846501916607241</v>
+        <v>1.93043382190757</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06130601590001185</v>
+        <v>0.0605200413371912</v>
       </c>
       <c r="W79">
-        <v>0.2213440414507772</v>
+        <v>0.2215293742526903</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2786637086364175</v>
+        <v>0.2750910969872327</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.20125822450459</v>
+        <v>0.20315822450459</v>
       </c>
       <c r="C80">
-        <v>-216.9308394186152</v>
+        <v>-222.1700810917947</v>
       </c>
       <c r="D80">
-        <v>96.25716058138482</v>
+        <v>95.26391890820526</v>
       </c>
       <c r="E80">
-        <v>201.988</v>
+        <v>206.234</v>
       </c>
       <c r="F80">
-        <v>331.188</v>
+        <v>335.434</v>
       </c>
       <c r="G80">
         <v>18</v>
@@ -7847,37 +7847,37 @@
         <v>21.483</v>
       </c>
       <c r="M80">
-        <v>78.0941304</v>
+        <v>79.0953372</v>
       </c>
       <c r="N80">
-        <v>-56.6111304</v>
+        <v>-57.61233720000001</v>
       </c>
       <c r="O80">
-        <v>-12.454448688</v>
+        <v>-12.674714184</v>
       </c>
       <c r="P80">
-        <v>-44.156681712</v>
+        <v>-44.937623016</v>
       </c>
       <c r="Q80">
-        <v>-43.239681712</v>
+        <v>-44.020623016</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1293877844885978</v>
+        <v>0.133368155178531</v>
       </c>
       <c r="T80">
-        <v>1.93043382190757</v>
+        <v>2.022359241998407</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0605200413371912</v>
+        <v>0.05975396486456852</v>
       </c>
       <c r="W80">
-        <v>0.2215293742526903</v>
+        <v>0.2217100150849348</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2750910969872327</v>
+        <v>0.2716089312025841</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.20315822450459</v>
+        <v>0.20505822450459</v>
       </c>
       <c r="C81">
-        <v>-222.1700810917947</v>
+        <v>-227.3890343343155</v>
       </c>
       <c r="D81">
-        <v>95.26391890820526</v>
+        <v>94.2909656656845</v>
       </c>
       <c r="E81">
-        <v>206.234</v>
+        <v>210.48</v>
       </c>
       <c r="F81">
-        <v>335.434</v>
+        <v>339.68</v>
       </c>
       <c r="G81">
         <v>18</v>
@@ -7929,37 +7929,37 @@
         <v>21.483</v>
       </c>
       <c r="M81">
-        <v>79.0953372</v>
+        <v>80.09654400000001</v>
       </c>
       <c r="N81">
-        <v>-57.61233720000001</v>
+        <v>-58.61354400000001</v>
       </c>
       <c r="O81">
-        <v>-12.674714184</v>
+        <v>-12.89497968</v>
       </c>
       <c r="P81">
-        <v>-44.937623016</v>
+        <v>-45.71856432000001</v>
       </c>
       <c r="Q81">
-        <v>-44.020623016</v>
+        <v>-44.80156432000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.133368155178531</v>
+        <v>0.1377465629374576</v>
       </c>
       <c r="T81">
-        <v>2.022359241998407</v>
+        <v>2.123477204098327</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05975396486456852</v>
+        <v>0.05900704030376141</v>
       </c>
       <c r="W81">
-        <v>0.2217100150849348</v>
+        <v>0.2218861398963731</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2716089312025841</v>
+        <v>0.2682138195625519</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.20505822450459</v>
+        <v>0.20695822450459</v>
       </c>
       <c r="C82">
-        <v>-227.3890343343155</v>
+        <v>-232.5883144933086</v>
       </c>
       <c r="D82">
-        <v>94.2909656656845</v>
+        <v>93.33768550669139</v>
       </c>
       <c r="E82">
-        <v>210.48</v>
+        <v>214.726</v>
       </c>
       <c r="F82">
-        <v>339.68</v>
+        <v>343.926</v>
       </c>
       <c r="G82">
         <v>18</v>
@@ -8011,37 +8011,37 @@
         <v>21.483</v>
       </c>
       <c r="M82">
-        <v>80.09654400000001</v>
+        <v>81.0977508</v>
       </c>
       <c r="N82">
-        <v>-58.61354400000001</v>
+        <v>-59.6147508</v>
       </c>
       <c r="O82">
-        <v>-12.89497968</v>
+        <v>-13.115245176</v>
       </c>
       <c r="P82">
-        <v>-45.71856432000001</v>
+        <v>-46.499505624</v>
       </c>
       <c r="Q82">
-        <v>-44.80156432000001</v>
+        <v>-45.582505624</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1377465629374576</v>
+        <v>0.1425858557236396</v>
       </c>
       <c r="T82">
-        <v>2.123477204098327</v>
+        <v>2.235239162208766</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05900704030376141</v>
+        <v>0.05827855832470263</v>
       </c>
       <c r="W82">
-        <v>0.2218861398963731</v>
+        <v>0.2220579159470351</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2682138195625519</v>
+        <v>0.2649025378395574</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.20695822450459</v>
+        <v>0.20885822450459</v>
       </c>
       <c r="C83">
-        <v>-232.5883144933086</v>
+        <v>-237.7685122803713</v>
       </c>
       <c r="D83">
-        <v>93.33768550669139</v>
+        <v>92.40348771962873</v>
       </c>
       <c r="E83">
-        <v>214.726</v>
+        <v>218.972</v>
       </c>
       <c r="F83">
-        <v>343.926</v>
+        <v>348.172</v>
       </c>
       <c r="G83">
         <v>18</v>
@@ -8093,37 +8093,37 @@
         <v>21.483</v>
       </c>
       <c r="M83">
-        <v>81.0977508</v>
+        <v>82.09895760000001</v>
       </c>
       <c r="N83">
-        <v>-59.6147508</v>
+        <v>-60.61595760000001</v>
       </c>
       <c r="O83">
-        <v>-13.115245176</v>
+        <v>-13.335510672</v>
       </c>
       <c r="P83">
-        <v>-46.499505624</v>
+        <v>-47.280446928</v>
       </c>
       <c r="Q83">
-        <v>-45.582505624</v>
+        <v>-46.363446928</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1425858557236396</v>
+        <v>0.1479628477082862</v>
       </c>
       <c r="T83">
-        <v>2.235239162208766</v>
+        <v>2.359419115664808</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05827855832470263</v>
+        <v>0.05756784419879162</v>
       </c>
       <c r="W83">
-        <v>0.2220579159470351</v>
+        <v>0.222225502337925</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2649025378395574</v>
+        <v>0.2616720190854165</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.20885822450459</v>
+        <v>0.21075822450459</v>
       </c>
       <c r="C84">
-        <v>-237.7685122803713</v>
+        <v>-242.9301949922098</v>
       </c>
       <c r="D84">
-        <v>92.40348771962873</v>
+        <v>91.4878050077902</v>
       </c>
       <c r="E84">
-        <v>218.972</v>
+        <v>223.218</v>
       </c>
       <c r="F84">
-        <v>348.172</v>
+        <v>352.418</v>
       </c>
       <c r="G84">
         <v>18</v>
@@ -8175,37 +8175,37 @@
         <v>21.483</v>
       </c>
       <c r="M84">
-        <v>82.09895760000001</v>
+        <v>83.10016440000001</v>
       </c>
       <c r="N84">
-        <v>-60.61595760000001</v>
+        <v>-61.61716440000001</v>
       </c>
       <c r="O84">
-        <v>-13.335510672</v>
+        <v>-13.555776168</v>
       </c>
       <c r="P84">
-        <v>-47.280446928</v>
+        <v>-48.06138823200001</v>
       </c>
       <c r="Q84">
-        <v>-46.363446928</v>
+        <v>-47.14438823200001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1479628477082862</v>
+        <v>0.1539724269852442</v>
       </c>
       <c r="T84">
-        <v>2.359419115664808</v>
+        <v>2.498208475409797</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05756784419879162</v>
+        <v>0.05687425571446883</v>
       </c>
       <c r="W84">
-        <v>0.222225502337925</v>
+        <v>0.2223890505025283</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2616720190854165</v>
+        <v>0.2585193441566764</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.21075822450459</v>
+        <v>0.21265822450459</v>
       </c>
       <c r="C85">
-        <v>-242.9301949922098</v>
+        <v>-248.0739076594179</v>
       </c>
       <c r="D85">
-        <v>91.4878050077902</v>
+        <v>90.59009234058206</v>
       </c>
       <c r="E85">
-        <v>223.218</v>
+        <v>227.464</v>
       </c>
       <c r="F85">
-        <v>352.418</v>
+        <v>356.664</v>
       </c>
       <c r="G85">
         <v>18</v>
@@ -8257,37 +8257,37 @@
         <v>21.483</v>
       </c>
       <c r="M85">
-        <v>83.10016440000001</v>
+        <v>84.1013712</v>
       </c>
       <c r="N85">
-        <v>-61.61716440000001</v>
+        <v>-62.61837120000001</v>
       </c>
       <c r="O85">
-        <v>-13.555776168</v>
+        <v>-13.776041664</v>
       </c>
       <c r="P85">
-        <v>-48.06138823200001</v>
+        <v>-48.84232953600001</v>
       </c>
       <c r="Q85">
-        <v>-47.14438823200001</v>
+        <v>-47.92532953600001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1539724269852442</v>
+        <v>0.160733203671822</v>
       </c>
       <c r="T85">
-        <v>2.498208475409797</v>
+        <v>2.65434650512291</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05687425571446883</v>
+        <v>0.05619718124167754</v>
       </c>
       <c r="W85">
-        <v>0.2223890505025283</v>
+        <v>0.2225487046632124</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2585193441566764</v>
+        <v>0.255441732916716</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.21265822450459</v>
+        <v>0.2145582245045899</v>
       </c>
       <c r="C86">
-        <v>-248.0739076594179</v>
+        <v>-253.2001741282793</v>
       </c>
       <c r="D86">
-        <v>90.59009234058206</v>
+        <v>89.7098258717207</v>
       </c>
       <c r="E86">
-        <v>227.4639999999999</v>
+        <v>231.71</v>
       </c>
       <c r="F86">
-        <v>356.6639999999999</v>
+        <v>360.91</v>
       </c>
       <c r="G86">
         <v>18</v>
@@ -8339,37 +8339,37 @@
         <v>21.483</v>
       </c>
       <c r="M86">
-        <v>84.10137119999999</v>
+        <v>85.10257799999999</v>
       </c>
       <c r="N86">
-        <v>-62.61837119999999</v>
+        <v>-63.619578</v>
       </c>
       <c r="O86">
-        <v>-13.776041664</v>
+        <v>-13.99630716</v>
       </c>
       <c r="P86">
-        <v>-48.84232953599999</v>
+        <v>-49.62327084</v>
       </c>
       <c r="Q86">
-        <v>-47.92532953599999</v>
+        <v>-48.70627083999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.160733203671822</v>
+        <v>0.1683954172499434</v>
       </c>
       <c r="T86">
-        <v>2.654346505122908</v>
+        <v>2.831302938797768</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05619718124167754</v>
+        <v>0.05553603793295193</v>
       </c>
       <c r="W86">
-        <v>0.2225487046632124</v>
+        <v>0.2227046022554099</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2554417329167161</v>
+        <v>0.2524365360588724</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2145582245045899</v>
+        <v>0.21645822450459</v>
       </c>
       <c r="C87">
-        <v>-253.2001741282793</v>
+        <v>-258.3094980801047</v>
       </c>
       <c r="D87">
-        <v>89.7098258717207</v>
+        <v>88.8465019198952</v>
       </c>
       <c r="E87">
-        <v>231.71</v>
+        <v>235.956</v>
       </c>
       <c r="F87">
-        <v>360.91</v>
+        <v>365.1559999999999</v>
       </c>
       <c r="G87">
         <v>18</v>
@@ -8421,37 +8421,37 @@
         <v>21.483</v>
       </c>
       <c r="M87">
-        <v>85.10257799999999</v>
+        <v>86.10378479999999</v>
       </c>
       <c r="N87">
-        <v>-63.619578</v>
+        <v>-64.6207848</v>
       </c>
       <c r="O87">
-        <v>-13.99630716</v>
+        <v>-14.216572656</v>
       </c>
       <c r="P87">
-        <v>-49.62327084</v>
+        <v>-50.404212144</v>
       </c>
       <c r="Q87">
-        <v>-48.70627083999999</v>
+        <v>-49.487212144</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1683954172499434</v>
+        <v>0.1771522327677965</v>
       </c>
       <c r="T87">
-        <v>2.831302938797768</v>
+        <v>3.033538862997609</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05553603793295193</v>
+        <v>0.05489027005001063</v>
       </c>
       <c r="W87">
-        <v>0.2227046022554099</v>
+        <v>0.2228568743222075</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2524365360588724</v>
+        <v>0.2495012275000482</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.21645822450459</v>
+        <v>0.21835822450459</v>
       </c>
       <c r="C88">
-        <v>-258.3094980801047</v>
+        <v>-263.402363992274</v>
       </c>
       <c r="D88">
-        <v>88.8465019198952</v>
+        <v>87.99963600772595</v>
       </c>
       <c r="E88">
-        <v>235.956</v>
+        <v>240.202</v>
       </c>
       <c r="F88">
-        <v>365.1559999999999</v>
+        <v>369.402</v>
       </c>
       <c r="G88">
         <v>18</v>
@@ -8503,37 +8503,37 @@
         <v>21.483</v>
       </c>
       <c r="M88">
-        <v>86.10378479999999</v>
+        <v>87.10499160000001</v>
       </c>
       <c r="N88">
-        <v>-64.6207848</v>
+        <v>-65.6219916</v>
       </c>
       <c r="O88">
-        <v>-14.216572656</v>
+        <v>-14.436838152</v>
       </c>
       <c r="P88">
-        <v>-50.404212144</v>
+        <v>-51.185153448</v>
       </c>
       <c r="Q88">
-        <v>-49.487212144</v>
+        <v>-50.268153448</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1771522327677965</v>
+        <v>0.1872562506730116</v>
       </c>
       <c r="T88">
-        <v>3.033538862997609</v>
+        <v>3.266888006305118</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05489027005001063</v>
+        <v>0.05425934740575762</v>
       </c>
       <c r="W88">
-        <v>0.2228568743222075</v>
+        <v>0.2230056458817224</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2495012275000482</v>
+        <v>0.2466333972988983</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.21835822450459</v>
+        <v>0.22025822450459</v>
       </c>
       <c r="C89">
-        <v>-263.402363992274</v>
+        <v>-268.4792380448325</v>
       </c>
       <c r="D89">
-        <v>87.99963600772595</v>
+        <v>87.1687619551675</v>
       </c>
       <c r="E89">
-        <v>240.202</v>
+        <v>244.448</v>
       </c>
       <c r="F89">
-        <v>369.402</v>
+        <v>373.648</v>
       </c>
       <c r="G89">
         <v>18</v>
@@ -8585,37 +8585,37 @@
         <v>21.483</v>
       </c>
       <c r="M89">
-        <v>87.10499160000001</v>
+        <v>88.1061984</v>
       </c>
       <c r="N89">
-        <v>-65.6219916</v>
+        <v>-66.62319840000001</v>
       </c>
       <c r="O89">
-        <v>-14.436838152</v>
+        <v>-14.657103648</v>
       </c>
       <c r="P89">
-        <v>-51.185153448</v>
+        <v>-51.966094752</v>
       </c>
       <c r="Q89">
-        <v>-50.268153448</v>
+        <v>-51.049094752</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.1872562506730116</v>
+        <v>0.1990442715624293</v>
       </c>
       <c r="T89">
-        <v>3.266888006305118</v>
+        <v>3.539128673497212</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05425934740575762</v>
+        <v>0.05364276391251038</v>
       </c>
       <c r="W89">
-        <v>0.2230056458817224</v>
+        <v>0.2231510362694301</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2466333972988983</v>
+        <v>0.2438307450568653</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.22025822450459</v>
+        <v>0.22215822450459</v>
       </c>
       <c r="C90">
-        <v>-268.4792380448325</v>
+        <v>-273.54056897621</v>
       </c>
       <c r="D90">
-        <v>87.1687619551675</v>
+        <v>86.35343102378998</v>
       </c>
       <c r="E90">
-        <v>244.448</v>
+        <v>248.694</v>
       </c>
       <c r="F90">
-        <v>373.648</v>
+        <v>377.8939999999999</v>
       </c>
       <c r="G90">
         <v>18</v>
@@ -8667,37 +8667,37 @@
         <v>21.483</v>
       </c>
       <c r="M90">
-        <v>88.1061984</v>
+        <v>89.10740519999999</v>
       </c>
       <c r="N90">
-        <v>-66.62319840000001</v>
+        <v>-67.62440519999998</v>
       </c>
       <c r="O90">
-        <v>-14.657103648</v>
+        <v>-14.877369144</v>
       </c>
       <c r="P90">
-        <v>-51.966094752</v>
+        <v>-52.74703605599998</v>
       </c>
       <c r="Q90">
-        <v>-51.049094752</v>
+        <v>-51.83003605599998</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.1990442715624293</v>
+        <v>0.2129755689771956</v>
       </c>
       <c r="T90">
-        <v>3.539128673497212</v>
+        <v>3.86086764381514</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05364276391251038</v>
+        <v>0.05304003622810016</v>
       </c>
       <c r="W90">
-        <v>0.2231510362694301</v>
+        <v>0.223293159457414</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2438307450568653</v>
+        <v>0.2410910737640917</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.22215822450459</v>
+        <v>0.22405822450459</v>
       </c>
       <c r="C91">
-        <v>-273.54056897621</v>
+        <v>-278.5867888913606</v>
       </c>
       <c r="D91">
-        <v>86.35343102378998</v>
+        <v>85.5532111086394</v>
       </c>
       <c r="E91">
-        <v>248.694</v>
+        <v>252.94</v>
       </c>
       <c r="F91">
-        <v>377.8939999999999</v>
+        <v>382.14</v>
       </c>
       <c r="G91">
         <v>18</v>
@@ -8749,37 +8749,37 @@
         <v>21.483</v>
       </c>
       <c r="M91">
-        <v>89.10740519999999</v>
+        <v>90.10861199999999</v>
       </c>
       <c r="N91">
-        <v>-67.62440519999998</v>
+        <v>-68.62561199999999</v>
       </c>
       <c r="O91">
-        <v>-14.877369144</v>
+        <v>-15.09763464</v>
       </c>
       <c r="P91">
-        <v>-52.74703605599998</v>
+        <v>-53.52797735999999</v>
       </c>
       <c r="Q91">
-        <v>-51.83003605599998</v>
+        <v>-52.61097735999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2129755689771956</v>
+        <v>0.2296931258749152</v>
       </c>
       <c r="T91">
-        <v>3.86086764381514</v>
+        <v>4.246954408196654</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05304003622810016</v>
+        <v>0.05245070249223237</v>
       </c>
       <c r="W91">
-        <v>0.223293159457414</v>
+        <v>0.2234321243523316</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2410910737640917</v>
+        <v>0.2384122840556018</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.22405822450459</v>
+        <v>0.22595822450459</v>
       </c>
       <c r="C92">
-        <v>-278.5867888913606</v>
+        <v>-283.6183140253814</v>
       </c>
       <c r="D92">
-        <v>85.5532111086394</v>
+        <v>84.76768597461859</v>
       </c>
       <c r="E92">
-        <v>252.94</v>
+        <v>257.186</v>
       </c>
       <c r="F92">
-        <v>382.14</v>
+        <v>386.386</v>
       </c>
       <c r="G92">
         <v>18</v>
@@ -8831,37 +8831,37 @@
         <v>21.483</v>
       </c>
       <c r="M92">
-        <v>90.10861199999999</v>
+        <v>91.1098188</v>
       </c>
       <c r="N92">
-        <v>-68.62561199999999</v>
+        <v>-69.6268188</v>
       </c>
       <c r="O92">
-        <v>-15.09763464</v>
+        <v>-15.317900136</v>
       </c>
       <c r="P92">
-        <v>-53.52797735999999</v>
+        <v>-54.308918664</v>
       </c>
       <c r="Q92">
-        <v>-52.61097735999999</v>
+        <v>-53.39191866399999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2296931258749152</v>
+        <v>0.2501256954165724</v>
       </c>
       <c r="T92">
-        <v>4.246954408196654</v>
+        <v>4.718838231329617</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05245070249223237</v>
+        <v>0.05187432114616388</v>
       </c>
       <c r="W92">
-        <v>0.2234321243523316</v>
+        <v>0.2235680350737346</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2384122840556018</v>
+        <v>0.2357923688461996</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.22595822450459</v>
+        <v>0.22785822450459</v>
       </c>
       <c r="C93">
-        <v>-283.6183140253814</v>
+        <v>-288.6355454654467</v>
       </c>
       <c r="D93">
-        <v>84.76768597461859</v>
+        <v>83.99645453455328</v>
       </c>
       <c r="E93">
-        <v>257.186</v>
+        <v>261.432</v>
       </c>
       <c r="F93">
-        <v>386.386</v>
+        <v>390.632</v>
       </c>
       <c r="G93">
         <v>18</v>
@@ -8913,37 +8913,37 @@
         <v>21.483</v>
       </c>
       <c r="M93">
-        <v>91.1098188</v>
+        <v>92.1110256</v>
       </c>
       <c r="N93">
-        <v>-69.6268188</v>
+        <v>-70.6280256</v>
       </c>
       <c r="O93">
-        <v>-15.317900136</v>
+        <v>-15.538165632</v>
       </c>
       <c r="P93">
-        <v>-54.308918664</v>
+        <v>-55.089859968</v>
       </c>
       <c r="Q93">
-        <v>-53.39191866399999</v>
+        <v>-54.172859968</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2501256954165724</v>
+        <v>0.2756664073436441</v>
       </c>
       <c r="T93">
-        <v>4.718838231329617</v>
+        <v>5.30869301024582</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05187432114616388</v>
+        <v>0.05131046982935775</v>
       </c>
       <c r="W93">
-        <v>0.2235680350737346</v>
+        <v>0.2237009912142374</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2357923688461996</v>
+        <v>0.2332294083152625</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.22785822450459</v>
+        <v>0.22975822450459</v>
       </c>
       <c r="C94">
-        <v>-288.6355454654467</v>
+        <v>-293.6388698336874</v>
       </c>
       <c r="D94">
-        <v>83.99645453455328</v>
+        <v>83.23913016631261</v>
       </c>
       <c r="E94">
-        <v>261.432</v>
+        <v>265.678</v>
       </c>
       <c r="F94">
-        <v>390.632</v>
+        <v>394.878</v>
       </c>
       <c r="G94">
         <v>18</v>
@@ -8995,37 +8995,37 @@
         <v>21.483</v>
       </c>
       <c r="M94">
-        <v>92.1110256</v>
+        <v>93.1122324</v>
       </c>
       <c r="N94">
-        <v>-70.6280256</v>
+        <v>-71.62923240000001</v>
       </c>
       <c r="O94">
-        <v>-15.538165632</v>
+        <v>-15.758431128</v>
       </c>
       <c r="P94">
-        <v>-55.089859968</v>
+        <v>-55.87080127200001</v>
       </c>
       <c r="Q94">
-        <v>-54.172859968</v>
+        <v>-54.95380127200001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.2756664073436441</v>
+        <v>0.3085044655355932</v>
       </c>
       <c r="T94">
-        <v>5.30869301024582</v>
+        <v>6.067077725995223</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05131046982935775</v>
+        <v>0.05075874434732165</v>
       </c>
       <c r="W94">
-        <v>0.2237009912142374</v>
+        <v>0.2238310880829016</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2332294083152625</v>
+        <v>0.2307215652150983</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.22975822450459</v>
+        <v>0.23165822450459</v>
       </c>
       <c r="C95">
-        <v>-293.6388698336874</v>
+        <v>-298.6286599334587</v>
       </c>
       <c r="D95">
-        <v>83.23913016631261</v>
+        <v>82.4953400665413</v>
       </c>
       <c r="E95">
-        <v>265.678</v>
+        <v>269.924</v>
       </c>
       <c r="F95">
-        <v>394.878</v>
+        <v>399.124</v>
       </c>
       <c r="G95">
         <v>18</v>
@@ -9077,37 +9077,37 @@
         <v>21.483</v>
       </c>
       <c r="M95">
-        <v>93.1122324</v>
+        <v>94.1134392</v>
       </c>
       <c r="N95">
-        <v>-71.62923240000001</v>
+        <v>-72.63043920000001</v>
       </c>
       <c r="O95">
-        <v>-15.758431128</v>
+        <v>-15.978696624</v>
       </c>
       <c r="P95">
-        <v>-55.87080127200001</v>
+        <v>-56.65174257600001</v>
       </c>
       <c r="Q95">
-        <v>-54.95380127200001</v>
+        <v>-55.73474257600001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3085044655355932</v>
+        <v>0.3522885431248589</v>
       </c>
       <c r="T95">
-        <v>6.067077725995223</v>
+        <v>7.078257346994429</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05075874434732165</v>
+        <v>0.05021875770532886</v>
       </c>
       <c r="W95">
-        <v>0.2238310880829016</v>
+        <v>0.2239584169330835</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2307215652150983</v>
+        <v>0.2282670804787674</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.23165822450459</v>
+        <v>0.23355822450459</v>
       </c>
       <c r="C96">
-        <v>-298.6286599334587</v>
+        <v>-303.6052753612665</v>
       </c>
       <c r="D96">
-        <v>82.4953400665413</v>
+        <v>81.76472463873344</v>
       </c>
       <c r="E96">
-        <v>269.924</v>
+        <v>274.17</v>
       </c>
       <c r="F96">
-        <v>399.124</v>
+        <v>403.37</v>
       </c>
       <c r="G96">
         <v>18</v>
@@ -9159,37 +9159,37 @@
         <v>21.483</v>
       </c>
       <c r="M96">
-        <v>94.1134392</v>
+        <v>95.11464600000001</v>
       </c>
       <c r="N96">
-        <v>-72.63043920000001</v>
+        <v>-73.63164600000002</v>
       </c>
       <c r="O96">
-        <v>-15.978696624</v>
+        <v>-16.19896212</v>
       </c>
       <c r="P96">
-        <v>-56.65174257600001</v>
+        <v>-57.43268388000001</v>
       </c>
       <c r="Q96">
-        <v>-55.73474257600001</v>
+        <v>-56.51568388000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3522885431248589</v>
+        <v>0.4135862517498308</v>
       </c>
       <c r="T96">
-        <v>7.078257346994429</v>
+        <v>8.493908816393319</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05021875770532886</v>
+        <v>0.0496901392031675</v>
       </c>
       <c r="W96">
-        <v>0.2239584169330835</v>
+        <v>0.2240830651758931</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2282670804787674</v>
+        <v>0.2258642691053068</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.23355822450459</v>
+        <v>0.23545822450459</v>
       </c>
       <c r="C97">
-        <v>-303.6052753612665</v>
+        <v>-308.5690630864622</v>
       </c>
       <c r="D97">
-        <v>81.76472463873344</v>
+        <v>81.04693691353781</v>
       </c>
       <c r="E97">
-        <v>274.17</v>
+        <v>278.416</v>
       </c>
       <c r="F97">
-        <v>403.37</v>
+        <v>407.616</v>
       </c>
       <c r="G97">
         <v>18</v>
@@ -9241,37 +9241,37 @@
         <v>21.483</v>
       </c>
       <c r="M97">
-        <v>95.11464600000001</v>
+        <v>96.1158528</v>
       </c>
       <c r="N97">
-        <v>-73.63164600000002</v>
+        <v>-74.63285279999999</v>
       </c>
       <c r="O97">
-        <v>-16.19896212</v>
+        <v>-16.419227616</v>
       </c>
       <c r="P97">
-        <v>-57.43268388000001</v>
+        <v>-58.21362518399999</v>
       </c>
       <c r="Q97">
-        <v>-56.51568388000001</v>
+        <v>-57.29662518399999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4135862517498308</v>
+        <v>0.5055328146872886</v>
       </c>
       <c r="T97">
-        <v>8.493908816393319</v>
+        <v>10.61738602049165</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0496901392031675</v>
+        <v>0.04917253358646784</v>
       </c>
       <c r="W97">
-        <v>0.2240830651758931</v>
+        <v>0.2242051165803109</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2258642691053068</v>
+        <v>0.2235115163021266</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.23545822450459</v>
+        <v>0.2373582245045899</v>
       </c>
       <c r="C98">
-        <v>-308.5690630864621</v>
+        <v>-313.5203580006685</v>
       </c>
       <c r="D98">
-        <v>81.04693691353781</v>
+        <v>80.34164199933146</v>
       </c>
       <c r="E98">
-        <v>278.4159999999999</v>
+        <v>282.662</v>
       </c>
       <c r="F98">
-        <v>407.6159999999999</v>
+        <v>411.862</v>
       </c>
       <c r="G98">
         <v>18</v>
@@ -9323,37 +9323,37 @@
         <v>21.483</v>
       </c>
       <c r="M98">
-        <v>96.11585279999998</v>
+        <v>97.11705959999999</v>
       </c>
       <c r="N98">
-        <v>-74.63285279999999</v>
+        <v>-75.6340596</v>
       </c>
       <c r="O98">
-        <v>-16.419227616</v>
+        <v>-16.639493112</v>
       </c>
       <c r="P98">
-        <v>-58.21362518399999</v>
+        <v>-58.994566488</v>
       </c>
       <c r="Q98">
-        <v>-57.29662518399999</v>
+        <v>-58.077566488</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5055328146872874</v>
+        <v>0.6587770862497165</v>
       </c>
       <c r="T98">
-        <v>10.61738602049162</v>
+        <v>14.15651469398883</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04917253358646785</v>
+        <v>0.04866560025052488</v>
       </c>
       <c r="W98">
-        <v>0.2242051165803109</v>
+        <v>0.2243246514609262</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2235115163021265</v>
+        <v>0.2212072738660221</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2373582245045899</v>
+        <v>0.23925822450459</v>
       </c>
       <c r="C99">
-        <v>-313.5203580006685</v>
+        <v>-318.4594834387668</v>
       </c>
       <c r="D99">
-        <v>80.34164199933146</v>
+        <v>79.64851656123317</v>
       </c>
       <c r="E99">
-        <v>282.662</v>
+        <v>286.908</v>
       </c>
       <c r="F99">
-        <v>411.862</v>
+        <v>416.1079999999999</v>
       </c>
       <c r="G99">
         <v>18</v>
@@ -9405,37 +9405,37 @@
         <v>21.483</v>
       </c>
       <c r="M99">
-        <v>97.11705959999999</v>
+        <v>98.1182664</v>
       </c>
       <c r="N99">
-        <v>-75.6340596</v>
+        <v>-76.63526640000001</v>
       </c>
       <c r="O99">
-        <v>-16.639493112</v>
+        <v>-16.859758608</v>
       </c>
       <c r="P99">
-        <v>-58.994566488</v>
+        <v>-59.77550779200001</v>
       </c>
       <c r="Q99">
-        <v>-58.077566488</v>
+        <v>-58.858507792</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.6587770862497165</v>
+        <v>0.9652656293745748</v>
       </c>
       <c r="T99">
-        <v>14.15651469398883</v>
+        <v>21.23477204098325</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04866560025052488</v>
+        <v>0.04816901249286646</v>
       </c>
       <c r="W99">
-        <v>0.2243246514609262</v>
+        <v>0.2244417468541821</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2212072738660221</v>
+        <v>0.2189500567857565</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.23925822450459</v>
+        <v>0.24115822450459</v>
       </c>
       <c r="C100">
-        <v>-318.4594834387668</v>
+        <v>-323.3867516731455</v>
       </c>
       <c r="D100">
-        <v>79.64851656123317</v>
+        <v>78.96724832685449</v>
       </c>
       <c r="E100">
-        <v>286.908</v>
+        <v>291.154</v>
       </c>
       <c r="F100">
-        <v>416.1079999999999</v>
+        <v>420.354</v>
       </c>
       <c r="G100">
         <v>18</v>
@@ -9487,37 +9487,37 @@
         <v>21.483</v>
       </c>
       <c r="M100">
-        <v>98.1182664</v>
+        <v>99.1194732</v>
       </c>
       <c r="N100">
-        <v>-76.63526640000001</v>
+        <v>-77.63647320000001</v>
       </c>
       <c r="O100">
-        <v>-16.859758608</v>
+        <v>-17.080024104</v>
       </c>
       <c r="P100">
-        <v>-59.77550779200001</v>
+        <v>-60.55644909600001</v>
       </c>
       <c r="Q100">
-        <v>-58.858507792</v>
+        <v>-59.63944909600001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>0.9652656293745748</v>
+        <v>1.88473125874915</v>
       </c>
       <c r="T100">
-        <v>21.23477204098325</v>
+        <v>42.4695440819665</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04816901249286646</v>
+        <v>0.04768245681112033</v>
       </c>
       <c r="W100">
-        <v>0.2244417468541821</v>
+        <v>0.2245564766839378</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2189500567857565</v>
+        <v>0.2167384400505469</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.24115822450459</v>
-      </c>
-      <c r="C101">
-        <v>-323.3867516731455</v>
-      </c>
-      <c r="D101">
-        <v>78.96724832685449</v>
-      </c>
-      <c r="E101">
-        <v>291.154</v>
-      </c>
-      <c r="F101">
-        <v>420.354</v>
-      </c>
-      <c r="G101">
-        <v>18</v>
-      </c>
-      <c r="H101">
-        <v>295.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>22.4</v>
-      </c>
-      <c r="K101">
-        <v>0.917</v>
-      </c>
-      <c r="L101">
-        <v>21.483</v>
-      </c>
-      <c r="M101">
-        <v>99.1194732</v>
-      </c>
-      <c r="N101">
-        <v>-77.63647320000001</v>
-      </c>
-      <c r="O101">
-        <v>-17.080024104</v>
-      </c>
-      <c r="P101">
-        <v>-60.55644909600001</v>
-      </c>
-      <c r="Q101">
-        <v>-59.63944909600001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>1.88473125874915</v>
-      </c>
-      <c r="T101">
-        <v>42.4695440819665</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04768245681112033</v>
-      </c>
-      <c r="W101">
-        <v>0.2245564766839378</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2167384400505469</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
